--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366687785664654</v>
+        <v>1.366689726675101</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35922118050268</v>
+        <v>1.359224739680909</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356279688472947</v>
+        <v>1.35628397753054</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350452616105098</v>
+        <v>1.350458794465618</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.34815886989615</v>
+        <v>1.348165315487423</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343988695703006</v>
+        <v>1.343995377286359</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339552746398607</v>
+        <v>1.339559570283388</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337096265689725</v>
+        <v>1.337103156591057</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339982605541442</v>
+        <v>1.339987074655087</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334062626585999</v>
+        <v>1.334062102878516</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334976592047587</v>
+        <v>1.334975963435392</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332800197785386</v>
+        <v>1.332799459613273</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.33237386767918</v>
+        <v>1.332371323142156</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329757191329101</v>
+        <v>1.329755089911969</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327931141375204</v>
+        <v>1.327929416634877</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331239328502835</v>
+        <v>1.33123797266033</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329458991908384</v>
+        <v>1.329460259977233</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324346497338577</v>
+        <v>1.324349748462692</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319567209321843</v>
+        <v>1.319571858640938</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31945158159381</v>
+        <v>1.31946017893996</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31660815151624</v>
+        <v>1.316615531925019</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320373116569346</v>
+        <v>1.320378655512722</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318683677624327</v>
+        <v>1.318679663036262</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313034371168437</v>
+        <v>1.313024604008241</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310644047518065</v>
+        <v>1.310628712721822</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303786982728603</v>
+        <v>1.303768216860191</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293993952599741</v>
+        <v>1.293971076458877</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.29045420994397</v>
+        <v>1.290427423335481</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294815395887713</v>
+        <v>1.294789070620197</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311565069644326</v>
+        <v>1.311521916625751</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324269536163112</v>
+        <v>1.324224059116939</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356199813934837</v>
+        <v>1.356175065511988</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374660035458465</v>
+        <v>1.374655634501205</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380308443361249</v>
+        <v>1.380310544305529</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389602655894179</v>
+        <v>1.389612155961878</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391314503390628</v>
+        <v>1.391328143097957</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389790858650147</v>
+        <v>1.389813138186286</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389427466089628</v>
+        <v>1.38945732001408</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394216851795245</v>
+        <v>1.394267807883226</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390618038847561</v>
+        <v>1.390673341977006</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394347520368476</v>
+        <v>1.394407839562734</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376797863369936</v>
+        <v>1.376842517474826</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371890316505871</v>
+        <v>1.371933115759964</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358395520967452</v>
+        <v>1.358421508148818</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339478016464232</v>
+        <v>1.339480583480936</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330386672670901</v>
+        <v>1.330370845638481</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336436456502679</v>
+        <v>1.336425989674801</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338455391516559</v>
+        <v>1.338448670769233</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339246580232523</v>
+        <v>1.339239162815605</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340683926411407</v>
+        <v>1.340681885877301</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340453599163894</v>
+        <v>1.340455642403132</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342600185633768</v>
+        <v>1.342605951846165</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341990582773648</v>
+        <v>1.341996336673264</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343358062768398</v>
+        <v>1.343363420100501</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341662704366513</v>
+        <v>1.341671001568352</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341325807887686</v>
+        <v>1.341332770697345</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343348796054139</v>
+        <v>1.343351061645622</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347053738547387</v>
+        <v>1.347049881225866</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350667522132863</v>
+        <v>1.350654349546748</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352196508354585</v>
+        <v>1.352177217625166</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350773436165726</v>
+        <v>1.350782903754713</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348860448470888</v>
+        <v>1.348924710333374</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346466460479829</v>
+        <v>1.346566763632497</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345921042302126</v>
+        <v>1.346025004810345</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347253669071548</v>
+        <v>1.347348971443882</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348818877837676</v>
+        <v>1.348887029395745</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.350959754708442</v>
+        <v>1.350983855028178</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.350842334611154</v>
+        <v>1.35088060644736</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351288427421895</v>
+        <v>1.351301781345513</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.352819479017216</v>
+        <v>1.352710921582049</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.356786463137595</v>
+        <v>1.356338376876247</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.357857365247346</v>
+        <v>1.357080204298675</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.346566122876506</v>
+        <v>1.346336646044928</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.343803518989225</v>
+        <v>1.343922236310263</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366689726675101</v>
+        <v>1.366691626826746</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359224739680909</v>
+        <v>1.359228224090348</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35628397753054</v>
+        <v>1.356288176839891</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350458794465618</v>
+        <v>1.350464843453357</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348165315487423</v>
+        <v>1.34817162607341</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343995377286359</v>
+        <v>1.344001918882195</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339559570283388</v>
+        <v>1.339566251185668</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337103156591057</v>
+        <v>1.337109903119692</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339987074655087</v>
+        <v>1.339991451949348</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334062102878516</v>
+        <v>1.334061591017056</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334975963435392</v>
+        <v>1.334975348898062</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332799459613273</v>
+        <v>1.332798737837011</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332371323142156</v>
+        <v>1.332368833228389</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329755089911969</v>
+        <v>1.329753033301152</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327929416634877</v>
+        <v>1.327927728321094</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.33123797266033</v>
+        <v>1.331236645404427</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329460259977233</v>
+        <v>1.329461500168773</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324349748462692</v>
+        <v>1.324352929851709</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319571858640938</v>
+        <v>1.319576408528035</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31946017893996</v>
+        <v>1.319468596223638</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316615531925019</v>
+        <v>1.316622761825153</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320378655512722</v>
+        <v>1.32038408521289</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318679663036262</v>
+        <v>1.318675738544285</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313024604008241</v>
+        <v>1.313015048487055</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310628712721822</v>
+        <v>1.310613707263011</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303768216860191</v>
+        <v>1.303749852130484</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293971076458877</v>
+        <v>1.293948687762448</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290427423335481</v>
+        <v>1.290401205711013</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294789070620197</v>
+        <v>1.294763299596564</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311521916625751</v>
+        <v>1.311479658190321</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324224059116939</v>
+        <v>1.324179524754609</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356175065511988</v>
+        <v>1.356150821364769</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374655634501205</v>
+        <v>1.374651321186113</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380310544305529</v>
+        <v>1.380312591507902</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389612155961878</v>
+        <v>1.389621441418652</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391328143097957</v>
+        <v>1.391341472714973</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389813138186286</v>
+        <v>1.389834924756617</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.38945732001408</v>
+        <v>1.389486520309561</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394267807883226</v>
+        <v>1.394317694219918</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390673341977006</v>
+        <v>1.390727492068563</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394407839562734</v>
+        <v>1.394466909377863</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376842517474826</v>
+        <v>1.376886264531987</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371933115759964</v>
+        <v>1.371975055176772</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358421508148818</v>
+        <v>1.358446989929481</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339480583480936</v>
+        <v>1.339483112623829</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330370845638481</v>
+        <v>1.330355342899394</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336425989674801</v>
+        <v>1.336415737588081</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338448670769233</v>
+        <v>1.338442085746818</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339239162815605</v>
+        <v>1.339231890733971</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340681885877301</v>
+        <v>1.340679878465088</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340455642403132</v>
+        <v>1.340457631055964</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342605951846165</v>
+        <v>1.342611588704622</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341996336673264</v>
+        <v>1.342001964099751</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343363420100501</v>
+        <v>1.343368675025516</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341671001568352</v>
+        <v>1.341679134037251</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341332770697345</v>
+        <v>1.341339602080494</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343351061645622</v>
+        <v>1.343353298706466</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347049881225866</v>
+        <v>1.347046120980557</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350654349546748</v>
+        <v>1.350641467949502</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352177217625166</v>
+        <v>1.352158324844501</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350782903754713</v>
+        <v>1.350762190006551</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348924710333374</v>
+        <v>1.349067716376101</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346566763632497</v>
+        <v>1.346769950179045</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.346025004810345</v>
+        <v>1.34626602944866</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347348971443882</v>
+        <v>1.347589093927266</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348887029395745</v>
+        <v>1.349126515615903</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.350983855028178</v>
+        <v>1.351221584026357</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.35088060644736</v>
+        <v>1.351186076236226</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351301781345513</v>
+        <v>1.351632014022698</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.352710921582049</v>
+        <v>1.352983561482731</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.356338376876247</v>
+        <v>1.356373436149269</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.357080204298675</v>
+        <v>1.356855633319928</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.346336646044928</v>
+        <v>1.346620131545926</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,15 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.343922236310263</v>
+        <v>1.344430099661687</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>1.347082544227109</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366691626826746</v>
+        <v>1.36669348739624</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359228224090348</v>
+        <v>1.35923163606237</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356288176839891</v>
+        <v>1.356292289188365</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350464843453357</v>
+        <v>1.350470767089</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.34817162607341</v>
+        <v>1.348177805850987</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344001918882195</v>
+        <v>1.344008324843495</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339566251185668</v>
+        <v>1.339572793551985</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337109903119692</v>
+        <v>1.33711650976497</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339991451949348</v>
+        <v>1.33999574022273</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334061591017056</v>
+        <v>1.334061090606016</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334975348898062</v>
+        <v>1.334974747969719</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332798737837011</v>
+        <v>1.33279803191775</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332368833228389</v>
+        <v>1.332366396198829</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329753033301152</v>
+        <v>1.329751020079792</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327927728321094</v>
+        <v>1.327926075292219</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331236645404427</v>
+        <v>1.331235345840804</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329461500168773</v>
+        <v>1.329462713390482</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324352929851709</v>
+        <v>1.324356043723091</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319576408528035</v>
+        <v>1.319580862136046</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319468596223638</v>
+        <v>1.319476839040953</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316622761825153</v>
+        <v>1.316629845766605</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32038408521289</v>
+        <v>1.320389408853809</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318675738544285</v>
+        <v>1.318671901164157</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313015048487055</v>
+        <v>1.313005697814739</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310613707263011</v>
+        <v>1.310599020664978</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303749852130484</v>
+        <v>1.303731875838982</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293948687762448</v>
+        <v>1.29392677112762</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290401205711013</v>
+        <v>1.290375539172352</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294763299596564</v>
+        <v>1.294738065521519</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311479658190321</v>
+        <v>1.31143826684275</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324179524754609</v>
+        <v>1.324135904104299</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356150821364769</v>
+        <v>1.35612706626429</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374651321186113</v>
+        <v>1.374647092941897</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380312591507902</v>
+        <v>1.380314586949778</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389621441418652</v>
+        <v>1.389630519421232</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391341472714973</v>
+        <v>1.39135450262174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389834924756617</v>
+        <v>1.389856234468684</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389486520309561</v>
+        <v>1.389515088118746</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394317694219918</v>
+        <v>1.394366544081321</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390727492068563</v>
+        <v>1.390780524730659</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394466909377863</v>
+        <v>1.394524768159822</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376886264531987</v>
+        <v>1.376929131832511</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371975055176772</v>
+        <v>1.372016160321307</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358446989929481</v>
+        <v>1.358471980812404</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339483112623829</v>
+        <v>1.339485604597338</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330355342899394</v>
+        <v>1.330340154613905</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336415737588081</v>
+        <v>1.33640569372158</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338442085746818</v>
+        <v>1.338435632399511</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339231890733971</v>
+        <v>1.339224759785496</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340679878465088</v>
+        <v>1.340677903444478</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340457631055964</v>
+        <v>1.340459567179356</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342611588704622</v>
+        <v>1.342617100490348</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342001964099751</v>
+        <v>1.342007469154153</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343368675025516</v>
+        <v>1.343373830404519</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341679134037251</v>
+        <v>1.341687106604986</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341339602080494</v>
+        <v>1.341346305669188</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343353298706466</v>
+        <v>1.343355507557946</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347046120980557</v>
+        <v>1.347042454354625</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350641467949502</v>
+        <v>1.350628867964917</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352158324844501</v>
+        <v>1.35213981807603</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350762190006551</v>
+        <v>1.350741854704117</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349067716376101</v>
+        <v>1.349253748677119</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346769950179045</v>
+        <v>1.347020813426858</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.34626602944866</v>
+        <v>1.346559301946011</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347589093927266</v>
+        <v>1.347893609077803</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349126515615903</v>
+        <v>1.349432449747938</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351221584026357</v>
+        <v>1.351534313492979</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351186076236226</v>
+        <v>1.351575048650969</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351632014022698</v>
+        <v>1.352069387421745</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.352983561482731</v>
+        <v>1.353396618120065</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.356373436149269</v>
+        <v>1.356644737911026</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.356855633319928</v>
+        <v>1.356997824955374</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.346620131545926</v>
+        <v>1.347394932029037</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.344430099661687</v>
+        <v>1.345764713228923</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.347082544227109</v>
+        <v>1.351423612491152</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36669348739624</v>
+        <v>1.366695309607596</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35923163606237</v>
+        <v>1.359234977832419</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356292289188365</v>
+        <v>1.356296317249106</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350470767089</v>
+        <v>1.350476569228363</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348177805850987</v>
+        <v>1.348183858844892</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344008324843495</v>
+        <v>1.344014599344646</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339572793551985</v>
+        <v>1.339579201646429</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.33711650976497</v>
+        <v>1.337122980832047</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.33999574022273</v>
+        <v>1.339999942161261</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334061090606016</v>
+        <v>1.334060601267148</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334974747969719</v>
+        <v>1.334974160204765</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33279803191775</v>
+        <v>1.332797341339944</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332366396198829</v>
+        <v>1.332364010387431</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329751020079792</v>
+        <v>1.329749048890104</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327926075292219</v>
+        <v>1.327924456453817</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331235345840804</v>
+        <v>1.331234073112046</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329462713390482</v>
+        <v>1.32946390051094</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324356043723091</v>
+        <v>1.324359092201367</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319580862136046</v>
+        <v>1.319585222486098</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319476839040953</v>
+        <v>1.319484912758586</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316629845766605</v>
+        <v>1.316636788118084</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320389408853809</v>
+        <v>1.320394629497598</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318671901164157</v>
+        <v>1.318668148041425</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313005697814739</v>
+        <v>1.312996545487965</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310599020664978</v>
+        <v>1.310584642889976</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303731875838982</v>
+        <v>1.303714275814723</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29392677112762</v>
+        <v>1.293905311810794</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290375539172352</v>
+        <v>1.290350406562573</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294738065521519</v>
+        <v>1.294713351810939</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31143826684275</v>
+        <v>1.311397716201591</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324135904104299</v>
+        <v>1.324093169367784</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.35612706626429</v>
+        <v>1.35610378558758</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374647092941897</v>
+        <v>1.374642947295964</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380314586949778</v>
+        <v>1.380316532518247</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389630519421232</v>
+        <v>1.389639396812978</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39135450262174</v>
+        <v>1.391367242742982</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389856234468684</v>
+        <v>1.389877082738719</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389515088118746</v>
+        <v>1.389543043685687</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394366544081321</v>
+        <v>1.394414389379926</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390780524730659</v>
+        <v>1.390832474123665</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394524768159822</v>
+        <v>1.394581452704226</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376929131832511</v>
+        <v>1.376971145586326</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372016160321307</v>
+        <v>1.372056455758726</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358471980812404</v>
+        <v>1.358496494755114</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339485604597338</v>
+        <v>1.339488060095508</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330340154613905</v>
+        <v>1.330325271335287</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33640569372158</v>
+        <v>1.336395851814905</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338435632399511</v>
+        <v>1.338429306836188</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339224759785496</v>
+        <v>1.33921776592732</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340677903444478</v>
+        <v>1.340675960102875</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340459567179356</v>
+        <v>1.340461452731434</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342617100490348</v>
+        <v>1.342622491298577</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342007469154153</v>
+        <v>1.342012855763007</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343373830404519</v>
+        <v>1.343378888995095</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341687106604986</v>
+        <v>1.341694923917211</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341346305669188</v>
+        <v>1.341352884965182</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343355507557946</v>
+        <v>1.343357688530236</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347042454354625</v>
+        <v>1.347038878048195</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350628867964917</v>
+        <v>1.350616540609324</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.35213981807603</v>
+        <v>1.352121685845807</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350741854704117</v>
+        <v>1.350721888013215</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349253748677119</v>
+        <v>1.349323921045701</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.347020813426858</v>
+        <v>1.347139341789097</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.346559301946011</v>
+        <v>1.346711878093585</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347893609077803</v>
+        <v>1.348034258027431</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349432449747938</v>
+        <v>1.349553776238865</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351534313492979</v>
+        <v>1.351633284154703</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351575048650969</v>
+        <v>1.351705902099395</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352069387421745</v>
+        <v>1.352187255619355</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353396618120065</v>
+        <v>1.353431303672545</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.356644737911026</v>
+        <v>1.356411251343093</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.356997824955374</v>
+        <v>1.356479514052279</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.347394932029037</v>
+        <v>1.347148077363295</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.345764713228923</v>
+        <v>1.345324349497321</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.351423612491152</v>
+        <v>1.347872949976251</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366695309607596</v>
+        <v>1.366697094634877</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359234977832419</v>
+        <v>1.359238251544904</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356296317249106</v>
+        <v>1.356300263586819</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350476569228363</v>
+        <v>1.350482253570758</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348183858844892</v>
+        <v>1.348189788916452</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344014599344646</v>
+        <v>1.344020746390506</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339579201646429</v>
+        <v>1.339585479559899</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337122980832047</v>
+        <v>1.337129320451232</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339999942161261</v>
+        <v>1.340004060344072</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334060601267148</v>
+        <v>1.334060122638615</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334974160204765</v>
+        <v>1.334973585176785</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332797341339944</v>
+        <v>1.332796665610105</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332364010387431</v>
+        <v>1.332361674197357</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329749048890104</v>
+        <v>1.329747118430332</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327924456453817</v>
+        <v>1.327922870756241</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331234073112046</v>
+        <v>1.331232826395757</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32946390051094</v>
+        <v>1.329465062361894</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324359092201367</v>
+        <v>1.324362077322949</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319585222486098</v>
+        <v>1.319589492474339</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319484912758586</v>
+        <v>1.319492822525419</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316636788118084</v>
+        <v>1.316643593075967</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320394629497598</v>
+        <v>1.32039975009027</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318668148041425</v>
+        <v>1.318664476444472</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312996545487965</v>
+        <v>1.312987585275256</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310584642889976</v>
+        <v>1.310570564316464</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303714275814723</v>
+        <v>1.303697040389016</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293905311810794</v>
+        <v>1.293884295674812</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290350406562573</v>
+        <v>1.290325791428144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294713351810939</v>
+        <v>1.294689142555737</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311397716201591</v>
+        <v>1.311357980943474</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324093169367784</v>
+        <v>1.324051293861692</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.35610378558758</v>
+        <v>1.356080965287816</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374642947295964</v>
+        <v>1.374638881869779</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380316532518247</v>
+        <v>1.380318430011544</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389639396812978</v>
+        <v>1.389648080140774</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391367242742982</v>
+        <v>1.391379702572651</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389877082738719</v>
+        <v>1.389897484328207</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389543043685687</v>
+        <v>1.389570406402881</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394414389379926</v>
+        <v>1.394461260733728</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390832474123665</v>
+        <v>1.390883373032604</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394581452704226</v>
+        <v>1.394636998333764</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376971145586326</v>
+        <v>1.377012330975067</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372056455758726</v>
+        <v>1.372095965102548</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358496494755114</v>
+        <v>1.358520545194874</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339488060095508</v>
+        <v>1.339490479801639</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330325271335287</v>
+        <v>1.330310683990449</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336395851814905</v>
+        <v>1.336386205855357</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338429306836188</v>
+        <v>1.338423105316749</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.33921776592732</v>
+        <v>1.339210905268438</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340675960102875</v>
+        <v>1.340674047745094</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340461452731434</v>
+        <v>1.340463289577208</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342622491298577</v>
+        <v>1.342627765048512</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342012855763007</v>
+        <v>1.342018127687479</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343378888995095</v>
+        <v>1.343383853455859</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341694923917211</v>
+        <v>1.341702590442291</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341352884965182</v>
+        <v>1.341359343345595</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343357688530236</v>
+        <v>1.343359841960911</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347038878048195</v>
+        <v>1.347035388909759</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350616540609324</v>
+        <v>1.350604477271547</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352121685845807</v>
+        <v>1.35210391712081</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350721888013215</v>
+        <v>1.350702280418063</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349323921045701</v>
+        <v>1.349344419508306</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.347139341789097</v>
+        <v>1.347204460718231</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.346711878093585</v>
+        <v>1.346808835175758</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.348034258027431</v>
+        <v>1.348108045222129</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349553776238865</v>
+        <v>1.349604381332356</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351633284154703</v>
+        <v>1.351649022363544</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351705902099395</v>
+        <v>1.351732728065012</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352187255619355</v>
+        <v>1.352179698484896</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353431303672545</v>
+        <v>1.353325053740304</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.356411251343093</v>
+        <v>1.356021135859592</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.356479514052279</v>
+        <v>1.355793598888683</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.347148077363295</v>
+        <v>1.346642952947766</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.345324349497321</v>
+        <v>1.344515491270823</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.347872949976251</v>
+        <v>1.344842116429345</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366697094634877</v>
+        <v>1.366698843604718</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359238251544904</v>
+        <v>1.359241459257783</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356300263586819</v>
+        <v>1.356304130663222</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350482253570758</v>
+        <v>1.350487823666847</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348189788916452</v>
+        <v>1.348195599771801</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344020746390506</v>
+        <v>1.34402676982492</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339585479559899</v>
+        <v>1.339591631218808</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337129320451232</v>
+        <v>1.337135532586785</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340004060344072</v>
+        <v>1.340008097248664</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334060122638615</v>
+        <v>1.33405965437412</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334973585176785</v>
+        <v>1.334973022477534</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332796665610105</v>
+        <v>1.332796004255639</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332361674197357</v>
+        <v>1.332359386097429</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329747118430332</v>
+        <v>1.329745227451887</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327922870756241</v>
+        <v>1.327921317192364</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331232826395757</v>
+        <v>1.331231604902799</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329465062361894</v>
+        <v>1.329466199740185</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324362077322949</v>
+        <v>1.324365001040641</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319589492474339</v>
+        <v>1.319593674878333</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319492822525419</v>
+        <v>1.319500573283474</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316643593075967</v>
+        <v>1.316650264672693</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32039975009027</v>
+        <v>1.320404773467154</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318664476444472</v>
+        <v>1.318660883758003</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312987585275256</v>
+        <v>1.312978811202958</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310570564316464</v>
+        <v>1.310556775717785</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303697040389016</v>
+        <v>1.303680158369844</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293884295674812</v>
+        <v>1.293863709158148</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290325791428144</v>
+        <v>1.290301677983311</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294689142555737</v>
+        <v>1.294665422487913</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311357980943474</v>
+        <v>1.31131903675066</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324051293861692</v>
+        <v>1.324010251962234</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356080965287816</v>
+        <v>1.356058591866278</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374638881869779</v>
+        <v>1.374634894374477</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380318430011544</v>
+        <v>1.380320281144135</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389648080140774</v>
+        <v>1.389656575670858</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391379702572651</v>
+        <v>1.391391891196922</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389897484328207</v>
+        <v>1.389917453378145</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389570406402881</v>
+        <v>1.389597194855422</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394461260733728</v>
+        <v>1.394507187531086</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390883373032604</v>
+        <v>1.390933252935528</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394636998333764</v>
+        <v>1.394691438971036</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377012330975067</v>
+        <v>1.377052712201883</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372095965102548</v>
+        <v>1.372134711060124</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358520545194874</v>
+        <v>1.358544145072499</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339490479801639</v>
+        <v>1.339492864387985</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330310683990449</v>
+        <v>1.330296383861696</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336386205855357</v>
+        <v>1.336376750065848</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338423105316749</v>
+        <v>1.338417024244902</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339210905268438</v>
+        <v>1.339204174062687</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340674047745094</v>
+        <v>1.340672165693065</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340463289577208</v>
+        <v>1.340465079493923</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342627765048512</v>
+        <v>1.342632925492645</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342018127687479</v>
+        <v>1.342023288531943</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343383853455859</v>
+        <v>1.343388726350749</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341702590442291</v>
+        <v>1.341710110479627</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341359343345595</v>
+        <v>1.341365684068298</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343359841960911</v>
+        <v>1.343361968193583</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347035388909759</v>
+        <v>1.347031983928142</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350604477271547</v>
+        <v>1.350592669694053</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.35210391712081</v>
+        <v>1.352086501288427</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350702280418063</v>
+        <v>1.350683022709601</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349344419508306</v>
+        <v>1.34936460580013</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.347204460718231</v>
+        <v>1.347268124565681</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.346808835175758</v>
+        <v>1.346904855184353</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.348108045222129</v>
+        <v>1.348195595456163</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349604381332356</v>
+        <v>1.349677943116363</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351649022363544</v>
+        <v>1.351698941211217</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351732728065012</v>
+        <v>1.351811270147979</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352179698484896</v>
+        <v>1.352250864954153</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353325053740304</v>
+        <v>1.353324719064461</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.356021135859592</v>
+        <v>1.355821048857858</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.355793598888683</v>
+        <v>1.355388232685805</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.346642952947766</v>
+        <v>1.346515588111061</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.344515491270823</v>
+        <v>1.34442774562753</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.344842116429345</v>
+        <v>1.344713113228226</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366698843604718</v>
+        <v>1.366700557598695</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359241459257783</v>
+        <v>1.359244602946873</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356304130663222</v>
+        <v>1.356307920842155</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350487823666847</v>
+        <v>1.350493282926039</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348195599771801</v>
+        <v>1.348201294969587</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.34402676982492</v>
+        <v>1.344032673338733</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339591631218808</v>
+        <v>1.339597660393265</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337135532586785</v>
+        <v>1.337141621045166</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340008097248664</v>
+        <v>1.34001205525586</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33405965437412</v>
+        <v>1.334059196142076</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334973022477534</v>
+        <v>1.334972471715979</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332796004255639</v>
+        <v>1.332795356823751</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332359386097429</v>
+        <v>1.332357144618789</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329745227451887</v>
+        <v>1.329743374756666</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327921317192364</v>
+        <v>1.327919794795448</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331231604902799</v>
+        <v>1.331230407875621</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329466199740185</v>
+        <v>1.329467313409553</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324365001040641</v>
+        <v>1.324367865227891</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319593674878333</v>
+        <v>1.319597772363057</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319500573283474</v>
+        <v>1.319508169778191</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316650264672693</v>
+        <v>1.316656806784685</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320404773467154</v>
+        <v>1.320409702358005</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318660883758003</v>
+        <v>1.318657367476943</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312978811202958</v>
+        <v>1.312970217542065</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310556775717785</v>
+        <v>1.310543268242154</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303680158369844</v>
+        <v>1.303663619017811</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293863709158148</v>
+        <v>1.293843539245964</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290301677983311</v>
+        <v>1.290278051076633</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294665422487913</v>
+        <v>1.294642176948626</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31131903675066</v>
+        <v>1.311280860261673</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324010251962234</v>
+        <v>1.323970019053199</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356058591866278</v>
+        <v>1.35603665234592</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374634894374477</v>
+        <v>1.374630982606722</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380320281144135</v>
+        <v>1.380322087551473</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389656575670858</v>
+        <v>1.38966488940364</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391391891196922</v>
+        <v>1.391403817315742</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389917453378145</v>
+        <v>1.389937003441191</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389597194855422</v>
+        <v>1.389623426862451</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394507187531086</v>
+        <v>1.394552197991739</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390933252935528</v>
+        <v>1.390982144067866</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394691438971036</v>
+        <v>1.394744807207108</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377052712201883</v>
+        <v>1.377092312538382</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372134711060124</v>
+        <v>1.372172715475526</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358544145072499</v>
+        <v>1.358567306854886</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339492864387985</v>
+        <v>1.339495214515534</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330296383861696</v>
+        <v>1.330282362569546</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336376750065848</v>
+        <v>1.336367478893503</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338417024244902</v>
+        <v>1.338411060161357</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339204174062687</v>
+        <v>1.339197568702131</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340672165693065</v>
+        <v>1.340670313285518</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340465079493923</v>
+        <v>1.340466824176049</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342632925492645</v>
+        <v>1.342637976225493</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342023288531943</v>
+        <v>1.342028341752026</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343388726350749</v>
+        <v>1.343393510153105</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341710110479627</v>
+        <v>1.341717488167534</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341365684068298</v>
+        <v>1.341371910277024</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343361968193583</v>
+        <v>1.343364067576687</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347031983928142</v>
+        <v>1.347028660224961</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350592669694053</v>
+        <v>1.350581109955227</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352086501288427</v>
+        <v>1.352069428137054</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350683022709601</v>
+        <v>1.350664105974239</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34936460580013</v>
+        <v>1.349433499737717</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.347268124565681</v>
+        <v>1.347387281227242</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.346904855184353</v>
+        <v>1.347054839879999</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.348195595456163</v>
+        <v>1.348343484578288</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349677943116363</v>
+        <v>1.349811935304729</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351698941211217</v>
+        <v>1.351813194451592</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351811270147979</v>
+        <v>1.351958335116192</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352250864954153</v>
+        <v>1.352402782153902</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353324719064461</v>
+        <v>1.353423100373209</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.355821048857858</v>
+        <v>1.355761175014083</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.355388232685805</v>
+        <v>1.355182361595294</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.346515588111061</v>
+        <v>1.346626527937098</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.34442774562753</v>
+        <v>1.344676582110887</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.344713113228226</v>
+        <v>1.345290437739112</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366700557598695</v>
+        <v>1.366702237655559</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359244602946873</v>
+        <v>1.35924768450991</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356307920842155</v>
+        <v>1.356311636394401</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350493282926039</v>
+        <v>1.350498634623437</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348201294969587</v>
+        <v>1.348206877928246</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344032673338733</v>
+        <v>1.344038460477323</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339597660393265</v>
+        <v>1.339603570704776</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337141621045166</v>
+        <v>1.337147589482813</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.34001205525586</v>
+        <v>1.340015936654469</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334059196142076</v>
+        <v>1.334058747624842</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334972471715979</v>
+        <v>1.334971932517404</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332795356823751</v>
+        <v>1.332794722880427</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332357144618789</v>
+        <v>1.332354948351757</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329743374756666</v>
+        <v>1.329741559194526</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327919794795448</v>
+        <v>1.32791830263714</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331230407875621</v>
+        <v>1.3312292345867</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329467313409553</v>
+        <v>1.329468404102343</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324367865227891</v>
+        <v>1.32437067168277</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319597772363057</v>
+        <v>1.31960178748655</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319508169778191</v>
+        <v>1.319515616568103</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316656806784685</v>
+        <v>1.316663223139805</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320409702358005</v>
+        <v>1.320414539391852</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318657367476943</v>
+        <v>1.318653925200709</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312970217542065</v>
+        <v>1.312961798795844</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310543268242154</v>
+        <v>1.310530033393836</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303663619017811</v>
+        <v>1.303647412023528</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293843539245964</v>
+        <v>1.293823773442884</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290278051076633</v>
+        <v>1.290254896159495</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294642176948626</v>
+        <v>1.294619391858153</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311280860261673</v>
+        <v>1.311243429024814</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323970019053199</v>
+        <v>1.32393057147697</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.35603665234592</v>
+        <v>1.356015134246465</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374630982606722</v>
+        <v>1.374627144444786</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380322087551473</v>
+        <v>1.380323850794424</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.38966488940364</v>
+        <v>1.389673027087603</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391403817315742</v>
+        <v>1.391415489263031</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389937003441191</v>
+        <v>1.389956147511838</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389623426862451</v>
+        <v>1.389649119516078</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394552197991739</v>
+        <v>1.394596319224223</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390982144067866</v>
+        <v>1.391030075483012</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394744807207108</v>
+        <v>1.394797134366095</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377092312538382</v>
+        <v>1.377131154368916</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372172715475526</v>
+        <v>1.372209999370041</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358567306854886</v>
+        <v>1.358590042556338</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339495214515534</v>
+        <v>1.339497530833829</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330282362569546</v>
+        <v>1.330268612056524</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336367478893503</v>
+        <v>1.336358386998923</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338411060161357</v>
+        <v>1.338405209737396</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339197568702131</v>
+        <v>1.339191085710785</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340670313285518</v>
+        <v>1.340668489877655</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340466824176049</v>
+        <v>1.340468525239936</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342637976225493</v>
+        <v>1.342642920691791</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342028341752026</v>
+        <v>1.342033290662176</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343393510153105</v>
+        <v>1.343398207249544</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341717488167534</v>
+        <v>1.341724727490669</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341371910277024</v>
+        <v>1.341378025006226</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343364067576687</v>
+        <v>1.343366140462375</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347028660224961</v>
+        <v>1.347025415047561</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350581109955227</v>
+        <v>1.350569790452679</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352069428137054</v>
+        <v>1.352052687837724</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350664105974239</v>
+        <v>1.350645521583018</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349433499737717</v>
+        <v>1.349411564717666</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.347387281227242</v>
+        <v>1.347382117690099</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.347054839879999</v>
+        <v>1.347040691999169</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.348343484578288</v>
+        <v>1.348315854031392</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349811935304729</v>
+        <v>1.349722689383671</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351813194451592</v>
+        <v>1.351644968384786</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351958335116192</v>
+        <v>1.351722122010962</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352402782153902</v>
+        <v>1.352065932445678</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353423100373209</v>
+        <v>1.352917092429468</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.355761175014083</v>
+        <v>1.354932612096362</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.355182361595294</v>
+        <v>1.353940315329677</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.346626527937098</v>
+        <v>1.345287166613417</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.344676582110887</v>
+        <v>1.342698608238047</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,15 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.345290437739112</v>
+        <v>1.341166432259731</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>1.325744557259731</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366702237655559</v>
+        <v>1.366703884773328</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35924768450991</v>
+        <v>1.359250705770369</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356311636394401</v>
+        <v>1.356315279502218</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350498634623437</v>
+        <v>1.350503881906394</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348206877928246</v>
+        <v>1.34821235193283</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344038460477323</v>
+        <v>1.344044134647698</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339603570704776</v>
+        <v>1.339609365633494</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337147589482813</v>
+        <v>1.337153441413461</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340015936654469</v>
+        <v>1.340019743645687</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334058747624842</v>
+        <v>1.334058308517997</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334971932517404</v>
+        <v>1.33497140452257</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332794722880427</v>
+        <v>1.332794102009467</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332354948351757</v>
+        <v>1.33235279594289</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329741559194526</v>
+        <v>1.329739779660907</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.32791830263714</v>
+        <v>1.327916839825584</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.3312292345867</v>
+        <v>1.331228084337062</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329468404102343</v>
+        <v>1.329469472521092</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32437067168277</v>
+        <v>1.324373422131729</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.31960178748655</v>
+        <v>1.319605722705214</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319515616568103</v>
+        <v>1.319522918033948</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316663223139805</v>
+        <v>1.316669517324395</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320414539391852</v>
+        <v>1.32041928710157</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318653925200709</v>
+        <v>1.318650554627841</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312961798795844</v>
+        <v>1.312953549688201</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310530033393836</v>
+        <v>1.310517063015451</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303647412023528</v>
+        <v>1.303631527486341</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293823773442884</v>
+        <v>1.29380439974738</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290254896159495</v>
+        <v>1.290232199256483</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294619391858153</v>
+        <v>1.294597053687609</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311243429024814</v>
+        <v>1.311206721454354</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.32393057147697</v>
+        <v>1.323891886488369</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356015134246465</v>
+        <v>1.355994025560895</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374627144444786</v>
+        <v>1.37462337784484</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380323850794424</v>
+        <v>1.380325572363416</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389673027087603</v>
+        <v>1.389680994232339</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391415489263031</v>
+        <v>1.391426915025638</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389956147511838</v>
+        <v>1.389974898054756</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389649119516078</v>
+        <v>1.389674289217963</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394596319224223</v>
+        <v>1.394639577279944</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391030075483012</v>
+        <v>1.391077075109417</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394797134366095</v>
+        <v>1.394848450566021</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377131154368916</v>
+        <v>1.377169259232353</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372209999370041</v>
+        <v>1.372246582980409</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358590042556338</v>
+        <v>1.358612363758754</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339497530833829</v>
+        <v>1.339499813980852</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330268612056524</v>
+        <v>1.330255124571883</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336358386998923</v>
+        <v>1.336349469246054</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338405209737396</v>
+        <v>1.338399469768802</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339191085710785</v>
+        <v>1.339184721738687</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340668489877655</v>
+        <v>1.340666694840815</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340468525239936</v>
+        <v>1.340470184228164</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342642920691791</v>
+        <v>1.342647762194182</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342033290662176</v>
+        <v>1.342038138442762</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343398207249544</v>
+        <v>1.343402819943648</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341724727490669</v>
+        <v>1.341731832287067</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341378025006226</v>
+        <v>1.341384031185702</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343366140462375</v>
+        <v>1.343368187205535</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347025415047561</v>
+        <v>1.347022245762392</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350569790452679</v>
+        <v>1.350558703887537</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352052687837724</v>
+        <v>1.35203627092672</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350645521583018</v>
+        <v>1.350627261181191</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349411564717666</v>
+        <v>1.349389993317526</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.347382117690099</v>
+        <v>1.347308883087426</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.347040691999169</v>
+        <v>1.346944178846468</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.348315854031392</v>
+        <v>1.348217089999156</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349722689383671</v>
+        <v>1.349546389830634</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351644968384786</v>
+        <v>1.35139297458796</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351722122010962</v>
+        <v>1.351398001887993</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352065932445678</v>
+        <v>1.351634997472678</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.352917092429468</v>
+        <v>1.352313626026029</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.354932612096362</v>
+        <v>1.354004695270284</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.353940315329677</v>
+        <v>1.352597598565996</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.345287166613417</v>
+        <v>1.343819359518292</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.342698608238047</v>
+        <v>1.340622070570003</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.341166432259731</v>
+        <v>1.337409963473233</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.325744557259731</v>
+        <v>1.321988088473233</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.347308883087426</v>
+        <v>1.347076485845534</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.346944178846468</v>
+        <v>1.346655783820104</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.348217089999156</v>
+        <v>1.347950373491939</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349546389830634</v>
+        <v>1.349256446349097</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.35139297458796</v>
+        <v>1.351068891080874</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351398001887993</v>
+        <v>1.351053495266721</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351634997472678</v>
+        <v>1.351243210533267</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.352313626026029</v>
+        <v>1.3518825027853</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.354004695270284</v>
+        <v>1.353476444393667</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.352597598565996</v>
+        <v>1.351934402142852</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.343819359518292</v>
+        <v>1.342933282210042</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.340622070570003</v>
+        <v>1.339402719119641</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.337409963473233</v>
+        <v>1.33516208693362</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.321988088473233</v>
+        <v>1.31768708693362</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366703884773328</v>
+        <v>1.366705499911273</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359250705770369</v>
+        <v>1.359253668481056</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356315279502218</v>
+        <v>1.356318852263609</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350503881906394</v>
+        <v>1.350509027800672</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.34821235193283</v>
+        <v>1.348217720141455</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344044134647698</v>
+        <v>1.344049699125181</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339609365633494</v>
+        <v>1.339615048525046</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337153441413461</v>
+        <v>1.337159180215033</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340019743645687</v>
+        <v>1.340023478347246</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334058308517997</v>
+        <v>1.33405787852966</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.33497140452257</v>
+        <v>1.334970887386928</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332794102009467</v>
+        <v>1.332793493811584</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.33235279594289</v>
+        <v>1.3323506860922</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329739779660907</v>
+        <v>1.329738035094601</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327916839825584</v>
+        <v>1.327915405503651</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331228084337062</v>
+        <v>1.331226956454903</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329469472521092</v>
+        <v>1.329470519340032</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324373422131729</v>
+        <v>1.32437611823312</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319605722705214</v>
+        <v>1.319609580378811</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319522918033948</v>
+        <v>1.319530078387248</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316669517324395</v>
+        <v>1.316675692789916</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32041928710157</v>
+        <v>1.32042394792821</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318650554627841</v>
+        <v>1.318647253550953</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312953549688201</v>
+        <v>1.312945465152745</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310517063015451</v>
+        <v>1.310504349271327</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303631527486341</v>
+        <v>1.303615955894312</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29380439974738</v>
+        <v>1.293785406627658</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290232199256483</v>
+        <v>1.290209946937485</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294597053687609</v>
+        <v>1.294575149432299</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311206721454354</v>
+        <v>1.311170716789234</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323891886488369</v>
+        <v>1.323853942211142</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355994025560895</v>
+        <v>1.355973314733273</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37462337784484</v>
+        <v>1.374619680837444</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380325572363416</v>
+        <v>1.380327253682308</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389680994232339</v>
+        <v>1.389688796120785</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391426915025638</v>
+        <v>1.391438102261125</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389974898054756</v>
+        <v>1.38999326703143</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389674289217963</v>
+        <v>1.389698951713719</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394639577279944</v>
+        <v>1.394681997204128</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391077075109417</v>
+        <v>1.391123169804404</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394848450566021</v>
+        <v>1.394898784776221</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377169259232353</v>
+        <v>1.377206647861537</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372246582980409</v>
+        <v>1.372282485794964</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358612363758754</v>
+        <v>1.358634281630767</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339499813980852</v>
+        <v>1.339502064582945</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330255124571883</v>
+        <v>1.330241892657187</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336349469246054</v>
+        <v>1.336340720692625</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338399469768802</v>
+        <v>1.338393837170126</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339184721738687</v>
+        <v>1.339178473556274</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340666694840815</v>
+        <v>1.340664927562126</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340470184228164</v>
+        <v>1.340471802613614</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342647762194182</v>
+        <v>1.342652503900439</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342038138442762</v>
+        <v>1.342042888146756</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343402819943648</v>
+        <v>1.343407350459463</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341731832287067</v>
+        <v>1.341738806254788</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341384031185702</v>
+        <v>1.34138993164498</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343368187205535</v>
+        <v>1.343370208162903</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347022245762392</v>
+        <v>1.347019149848784</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350558703887537</v>
+        <v>1.350547843249635</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.35203627092672</v>
+        <v>1.352020168289103</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350627261181191</v>
+        <v>1.35060931667819</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349389993317526</v>
+        <v>1.349368777047633</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.347076485845534</v>
+        <v>1.346710733088735</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.346655783820104</v>
+        <v>1.346197633541343</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347950373491939</v>
+        <v>1.347505440844519</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349256446349097</v>
+        <v>1.348727653919936</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351068891080874</v>
+        <v>1.350409625973069</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351053495266721</v>
+        <v>1.350299106781609</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351243210533267</v>
+        <v>1.350327924078085</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.3518825027853</v>
+        <v>1.350755351893915</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.353476444393667</v>
+        <v>1.351932115043018</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.351934402142852</v>
+        <v>1.349854966357163</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.342933282210042</v>
+        <v>1.340511040921147</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.339402719119641</v>
+        <v>1.336139519667847</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.33516208693362</v>
+        <v>1.329826028408583</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.31768708693362</v>
+        <v>1.298483071205872</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366705499911273</v>
+        <v>1.366707083991772</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359253668481056</v>
+        <v>1.359256574327507</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356318852263609</v>
+        <v>1.356322356696355</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350509027800672</v>
+        <v>1.350514075216265</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348217720141455</v>
+        <v>1.348222985591368</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344049699125181</v>
+        <v>1.344055157059709</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339615048525046</v>
+        <v>1.339620622596972</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337159180215033</v>
+        <v>1.337164809136138</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340023478347246</v>
+        <v>1.340027142797326</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33405787852966</v>
+        <v>1.334057457379857</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334970887386928</v>
+        <v>1.334970380779874</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332793493811584</v>
+        <v>1.332792897903554</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.3323506860922</v>
+        <v>1.332348617550546</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329738035094601</v>
+        <v>1.329736324475647</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327915405503651</v>
+        <v>1.327913998847258</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331226956454903</v>
+        <v>1.331225850294277</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329470519340032</v>
+        <v>1.329471545206501</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32437611823312</v>
+        <v>1.324378761580524</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319609580378811</v>
+        <v>1.319613362775165</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319530078387248</v>
+        <v>1.3195371016784</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316675692789916</v>
+        <v>1.316681752859223</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32042394792821</v>
+        <v>1.320428524225107</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318647253550953</v>
+        <v>1.318644019851995</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312945465152745</v>
+        <v>1.312937540322481</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310504349271327</v>
+        <v>1.310491884631812</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303615955894312</v>
+        <v>1.303600688105349</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293785406627658</v>
+        <v>1.293766782998936</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290209946937485</v>
+        <v>1.290188126291393</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294575149432299</v>
+        <v>1.294553666586614</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311170716789234</v>
+        <v>1.311135395054098</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323853942211142</v>
+        <v>1.323816717596905</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355973314733273</v>
+        <v>1.355952990637794</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374619680837444</v>
+        <v>1.374616051524225</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380327253682308</v>
+        <v>1.380328896112009</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389688796120785</v>
+        <v>1.389696437820725</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391438102261125</v>
+        <v>1.391449058314487</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.38999326703143</v>
+        <v>1.390011265925214</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389698951713719</v>
+        <v>1.389723122125291</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394681997204128</v>
+        <v>1.394723603083861</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391123169804404</v>
+        <v>1.391168385404926</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394898784776221</v>
+        <v>1.394948164871483</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377206647861537</v>
+        <v>1.377243340220547</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372282485794964</v>
+        <v>1.372317726587795</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358634281630767</v>
+        <v>1.358655806945874</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339502064582945</v>
+        <v>1.339504283254769</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330241892657187</v>
+        <v>1.330228909132687</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336340720692625</v>
+        <v>1.336332136581124</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338393837170126</v>
+        <v>1.338388308969251</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339178473556274</v>
+        <v>1.339172338049067</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340664927562126</v>
+        <v>1.340663187444157</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340471802613614</v>
+        <v>1.340473381803277</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342652503900439</v>
+        <v>1.342657148850259</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342042888146756</v>
+        <v>1.342047542706025</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343407350459463</v>
+        <v>1.343411800944834</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341738806254788</v>
+        <v>1.34174565295821</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.34138993164498</v>
+        <v>1.341395729117498</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343370208162903</v>
+        <v>1.343372203692271</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347019149848784</v>
+        <v>1.347016124893112</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350547843249635</v>
+        <v>1.350537201803561</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352020168289103</v>
+        <v>1.352004371143106</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.35060931667819</v>
+        <v>1.35059168023799</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349368777047633</v>
+        <v>1.349347907660639</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346710733088735</v>
+        <v>1.346361645355289</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.346197633541343</v>
+        <v>1.345755136953986</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347505440844519</v>
+        <v>1.347067394992251</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348727653919936</v>
+        <v>1.348210608185911</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.350409625973069</v>
+        <v>1.349781702269783</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.350299106781609</v>
+        <v>1.349597109966013</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.350327924078085</v>
+        <v>1.349496665982013</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.350755351893915</v>
+        <v>1.349739072210526</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.351932115043018</v>
+        <v>1.350539638468488</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.349854966357163</v>
+        <v>1.34798078035426</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.340511040921147</v>
+        <v>1.338334849436047</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.336139519667847</v>
+        <v>1.333225429214681</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.329826028408583</v>
+        <v>1.325346337055648</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.298483071205872</v>
+        <v>1.294764552662876</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366707083991772</v>
+        <v>1.366708637902073</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359256574327507</v>
+        <v>1.359259424931173</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356322356696355</v>
+        <v>1.356325794741805</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350514075216265</v>
+        <v>1.350519026952874</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348222985591368</v>
+        <v>1.348228151204677</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344055157059709</v>
+        <v>1.344060511481777</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339620622596972</v>
+        <v>1.339626090944792</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337164809136138</v>
+        <v>1.337170331302201</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340027142797326</v>
+        <v>1.340030738958259</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334057457379857</v>
+        <v>1.334057044799919</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334970380779874</v>
+        <v>1.334969884384054</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332792897903554</v>
+        <v>1.332792313917421</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332348617550546</v>
+        <v>1.332346589117173</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329736324475647</v>
+        <v>1.329734646823342</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327913998847258</v>
+        <v>1.327912619063797</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331225850294277</v>
+        <v>1.331224765233865</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329471545206501</v>
+        <v>1.329472550742262</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324378761580524</v>
+        <v>1.324381353705874</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319613362775165</v>
+        <v>1.319617072074593</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.3195371016784</v>
+        <v>1.319543991804303</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316681752859223</v>
+        <v>1.316687700732487</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320428524225107</v>
+        <v>1.320433018261755</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318644019851995</v>
+        <v>1.318640851497791</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312937540322481</v>
+        <v>1.31292977052012</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310491884631812</v>
+        <v>1.310479661858506</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303600688105349</v>
+        <v>1.30358571532944</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293766782998936</v>
+        <v>1.293748518202031</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290188126291393</v>
+        <v>1.290166724901327</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294553666586614</v>
+        <v>1.294532593120335</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311135395054098</v>
+        <v>1.311100737022518</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323816717596905</v>
+        <v>1.32378019238639</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355952990637794</v>
+        <v>1.355933042558987</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374616051524225</v>
+        <v>1.374612488074723</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380328896112009</v>
+        <v>1.380330500953878</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389696437820725</v>
+        <v>1.389703924195588</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391449058314487</v>
+        <v>1.391459790233859</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390011265925214</v>
+        <v>1.3900289057649</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389723122125291</v>
+        <v>1.389746814981422</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394723603083861</v>
+        <v>1.394764418093402</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391168385404926</v>
+        <v>1.391212746775487</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394948164871483</v>
+        <v>1.394996617683182</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377243340220547</v>
+        <v>1.377279355539924</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372317726587795</v>
+        <v>1.372352323451063</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358655806945874</v>
+        <v>1.358676950099636</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339504283254769</v>
+        <v>1.339506470599307</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330228909132687</v>
+        <v>1.330216167084462</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336332136581124</v>
+        <v>1.336323712330265</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338388308969251</v>
+        <v>1.338382882302275</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339172338049067</v>
+        <v>1.339166312212617</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340663187444157</v>
+        <v>1.340661473904566</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340473381803277</v>
+        <v>1.340474923141815</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342657148850259</v>
+        <v>1.342661699961639</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342047542706025</v>
+        <v>1.342052104937254</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343411800944834</v>
+        <v>1.343416173474578</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34174565295821</v>
+        <v>1.341752375833989</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341395729117498</v>
+        <v>1.341401426244584</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343372203692271</v>
+        <v>1.34337417415177</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347016124893112</v>
+        <v>1.347013168583296</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350537201803561</v>
+        <v>1.350526773075487</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352004371143106</v>
+        <v>1.351988871025336</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.35059168023799</v>
+        <v>1.350574344269836</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349347907660639</v>
+        <v>1.349327377144013</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346361645355289</v>
+        <v>1.346148591292294</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345755136953986</v>
+        <v>1.345478687550197</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347067394992251</v>
+        <v>1.346800865069747</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348210608185911</v>
+        <v>1.347851800655251</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.349781702269783</v>
+        <v>1.349358448514773</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.349597109966013</v>
+        <v>1.349119769325225</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.349496665982013</v>
+        <v>1.348926064658449</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.349739072210526</v>
+        <v>1.349017201780234</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.350539638468488</v>
+        <v>1.349514113394436</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.34798078035426</v>
+        <v>1.346578155059885</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.338334849436047</v>
+        <v>1.336769192131582</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.333225429214681</v>
+        <v>1.331179471720045</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.325346337055648</v>
+        <v>1.322538271610955</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.294764552662876</v>
+        <v>1.294317278007695</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366708637902073</v>
+        <v>1.366710162495945</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359259424931173</v>
+        <v>1.35926222185245</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356325794741805</v>
+        <v>1.356329168268465</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350519026952874</v>
+        <v>1.350523885705091</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348228151204677</v>
+        <v>1.348233219793753</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344060511481777</v>
+        <v>1.344065765308043</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339626090944792</v>
+        <v>1.33963145654774</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337170331302201</v>
+        <v>1.337175749721245</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340030738958259</v>
+        <v>1.340034268720017</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334057044799919</v>
+        <v>1.334056640531918</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334969884384054</v>
+        <v>1.334969397894709</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332792313917421</v>
+        <v>1.33279174149974</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332346589117173</v>
+        <v>1.332344599637392</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329734646823342</v>
+        <v>1.32973300119438</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327912619063797</v>
+        <v>1.327911265390642</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331224765233865</v>
+        <v>1.331223700675816</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329472550742262</v>
+        <v>1.329473536544759</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324381353705874</v>
+        <v>1.32438389608241</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319617072074593</v>
+        <v>1.31962071037408</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319543991804303</v>
+        <v>1.319550752515565</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316687700732487</v>
+        <v>1.316693539492801</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320433018261755</v>
+        <v>1.320437432227497</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318640851497791</v>
+        <v>1.318637746535847</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31292977052012</v>
+        <v>1.312922151248938</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310479661858506</v>
+        <v>1.310467673990336</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.30358571532944</v>
+        <v>1.303571029111886</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293748518202031</v>
+        <v>1.293730601983159</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290166724901327</v>
+        <v>1.290145730821246</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294532593120335</v>
+        <v>1.294511917456291</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311100737022518</v>
+        <v>1.311066724182263</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.32378019238639</v>
+        <v>1.323744347072858</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355933042558987</v>
+        <v>1.355913460173008</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374612488074723</v>
+        <v>1.374608988723413</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380330500953878</v>
+        <v>1.380332069452889</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389703924195588</v>
+        <v>1.389711259914619</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391459790233859</v>
+        <v>1.391470304785295</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.3900289057649</v>
+        <v>1.390046197146919</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389746814981422</v>
+        <v>1.389770044246381</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394764418093402</v>
+        <v>1.394804464536953</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391212746775487</v>
+        <v>1.391256277853367</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394996617683182</v>
+        <v>1.395044169047567</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377279355539924</v>
+        <v>1.377314712349979</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372352323451063</v>
+        <v>1.372386293825585</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358676950099636</v>
+        <v>1.358697721125985</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339506470599307</v>
+        <v>1.339508627207885</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330216167084462</v>
+        <v>1.330203659852253</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336323712330265</v>
+        <v>1.336315443526926</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338382882302275</v>
+        <v>1.338377554408641</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339166312212617</v>
+        <v>1.339160393147728</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340661473904566</v>
+        <v>1.340659786375745</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340474923141815</v>
+        <v>1.3404764279149</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342661699961639</v>
+        <v>1.342666160036889</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342052104937254</v>
+        <v>1.342056577547518</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343416173474578</v>
+        <v>1.343420470053497</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341752375833989</v>
+        <v>1.341758978196697</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341401426244584</v>
+        <v>1.34140702557923</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.34337417415177</v>
+        <v>1.343376119899237</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347013168583296</v>
+        <v>1.347010278703651</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350526773075487</v>
+        <v>1.350516550840748</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351988871025336</v>
+        <v>1.351973659776747</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350574344269836</v>
+        <v>1.350557301419328</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349327377144013</v>
+        <v>1.349307177712735</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346148591292294</v>
+        <v>1.346131092663858</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345478687550197</v>
+        <v>1.345215797578942</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.346800865069747</v>
+        <v>1.346460637900344</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.347851800655251</v>
+        <v>1.347447875557114</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.349358448514773</v>
+        <v>1.348881997500363</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.349119769325225</v>
+        <v>1.348588932784967</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.348926064658449</v>
+        <v>1.348318460965239</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.349017201780234</v>
+        <v>1.348274441087391</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.349514113394436</v>
+        <v>1.348474162890736</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.346578155059885</v>
+        <v>1.345240704952702</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.336769192131582</v>
+        <v>1.335140633771629</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.331179471720045</v>
+        <v>1.32910040339529</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.322538271610955</v>
+        <v>1.319800218687895</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,15 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.294317278007695</v>
+        <v>1.293153173132662</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>1.281796367699251</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366710162495945</v>
+        <v>1.366711658595249</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35926222185245</v>
+        <v>1.359264966593512</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356329168268465</v>
+        <v>1.356332479075381</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350523885705091</v>
+        <v>1.350528654067277</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348233219793753</v>
+        <v>1.348238194066335</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344065765308043</v>
+        <v>1.344070921346624</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33963145654774</v>
+        <v>1.339636722274168</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337175749721245</v>
+        <v>1.337181067289351</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340034268720017</v>
+        <v>1.340037733903518</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334056640531918</v>
+        <v>1.334056244328141</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334969397894709</v>
+        <v>1.334968921019058</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33279174149974</v>
+        <v>1.332791180310876</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332344599637392</v>
+        <v>1.332342648000391</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.32973300119438</v>
+        <v>1.329731386681079</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327911265390642</v>
+        <v>1.327909937093751</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331223700675816</v>
+        <v>1.331222656044643</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329473536544759</v>
+        <v>1.329474503188287</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32438389608241</v>
+        <v>1.324386390127458</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.31962071037408</v>
+        <v>1.319624279691226</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319550752515565</v>
+        <v>1.319557387423295</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316693539492801</v>
+        <v>1.316699272111475</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320437432227497</v>
+        <v>1.320441768235008</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318637746535847</v>
+        <v>1.318634703090397</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312922151248938</v>
+        <v>1.312914678184156</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310467673990336</v>
+        <v>1.310455914330416</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303571029111886</v>
+        <v>1.303556621317492</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293730601983159</v>
+        <v>1.293713024474877</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290145730821246</v>
+        <v>1.290125132553879</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294511917456291</v>
+        <v>1.294491628449255</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311066724182263</v>
+        <v>1.311033338702472</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323744347072858</v>
+        <v>1.32370916286751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355913460173008</v>
+        <v>1.355894233529934</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374608988723413</v>
+        <v>1.374605551766866</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380332069452889</v>
+        <v>1.380333602800621</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389711259914619</v>
+        <v>1.389718449462436</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391470304785295</v>
+        <v>1.39148060846667</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390046197146919</v>
+        <v>1.390063150256259</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389770044246381</v>
+        <v>1.389792823347021</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394804464536953</v>
+        <v>1.394843763889051</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391256277853367</v>
+        <v>1.391299001691377</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395044169047567</v>
+        <v>1.395090843851395</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377314712349979</v>
+        <v>1.377349428512303</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372386293825585</v>
+        <v>1.372419654529793</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358697721125985</v>
+        <v>1.358718129712709</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339508627207885</v>
+        <v>1.33951075366023</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330203659852253</v>
+        <v>1.330191381017968</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336315443526926</v>
+        <v>1.336307325918526</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338377554408641</v>
+        <v>1.338372322626546</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339160393147728</v>
+        <v>1.339154578055914</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340659786375745</v>
+        <v>1.340658124304466</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.3404764279149</v>
+        <v>1.340477897352347</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342666160036889</v>
+        <v>1.342670531768289</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342056577547518</v>
+        <v>1.342060963139546</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343420470053497</v>
+        <v>1.343424692619258</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341758978196697</v>
+        <v>1.341765463244178</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.34140702557923</v>
+        <v>1.341412529589701</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343376119899237</v>
+        <v>1.343378041291649</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347010278703651</v>
+        <v>1.34700745313002</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350516550840748</v>
+        <v>1.35050652911211</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351973659776747</v>
+        <v>1.35195872952933</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350557301419328</v>
+        <v>1.350540544559861</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349307177712735</v>
+        <v>1.349287301802204</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346131092663858</v>
+        <v>1.346113824952884</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345215797578942</v>
+        <v>1.34473992247614</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.346460637900344</v>
+        <v>1.345867615761168</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.347447875557114</v>
+        <v>1.346749390058719</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.348881997500363</v>
+        <v>1.348064074224525</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.348588932784967</v>
+        <v>1.347670008003989</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.348318460965239</v>
+        <v>1.34726765472291</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.348274441087391</v>
+        <v>1.347037594657167</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.348474162890736</v>
+        <v>1.346869672124757</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.345240704952702</v>
+        <v>1.343245151907867</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.335140633771629</v>
+        <v>1.332666745729547</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.32910040339529</v>
+        <v>1.32595424382128</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.319800218687895</v>
+        <v>1.31551985920037</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.293153173132662</v>
+        <v>1.288674101345932</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.281796367699251</v>
+        <v>1.270940351345932</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366711658595249</v>
+        <v>1.366713126991407</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359264966593512</v>
+        <v>1.359267660601013</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356332479075381</v>
+        <v>1.356335728895337</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350528654067277</v>
+        <v>1.350533334538186</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348238194066335</v>
+        <v>1.348243076630347</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344070921346624</v>
+        <v>1.344075982302098</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339636722274168</v>
+        <v>1.339641890886661</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337181067289351</v>
+        <v>1.337186286795818</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340037733903518</v>
+        <v>1.340041136263745</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334056244328141</v>
+        <v>1.334055855950586</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334968921019058</v>
+        <v>1.334968453475714</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332791180310876</v>
+        <v>1.332790630024333</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332342648000391</v>
+        <v>1.332340733137177</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329731386681079</v>
+        <v>1.329729802409722</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327909937093751</v>
+        <v>1.327908633466332</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331222656044643</v>
+        <v>1.331221630786195</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329474503188287</v>
+        <v>1.329475451225107</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324386390127458</v>
+        <v>1.324388837205058</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319624279691226</v>
+        <v>1.319627781967955</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319557387423295</v>
+        <v>1.319563900005532</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316699272111475</v>
+        <v>1.316704901453052</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320441768235008</v>
+        <v>1.320446028323608</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318634703090397</v>
+        <v>1.318631719358691</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312914678184156</v>
+        <v>1.31290734716482</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310455914330416</v>
+        <v>1.310444376433648</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303556621317492</v>
+        <v>1.303542484115637</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293713024474877</v>
+        <v>1.293695776178084</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290125132553879</v>
+        <v>1.290104919029889</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294491628449255</v>
+        <v>1.294471715366005</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311033338702472</v>
+        <v>1.311000563402632</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.32370916286751</v>
+        <v>1.323674621666796</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355894233529934</v>
+        <v>1.355875353037017</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374605551766866</v>
+        <v>1.374602175561074</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380333602800621</v>
+        <v>1.38033510213804</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389718449462436</v>
+        <v>1.389725497148041</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39148060846667</v>
+        <v>1.391490707520779</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390063150256259</v>
+        <v>1.390079774886169</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389792823347021</v>
+        <v>1.38981516519831</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394843763889051</v>
+        <v>1.394882336832738</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391299001691377</v>
+        <v>1.391340940498256</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395090843851395</v>
+        <v>1.395136666075087</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377349428512303</v>
+        <v>1.377383521249606</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372419654529793</v>
+        <v>1.372452421787167</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358718129712709</v>
+        <v>1.358738185216154</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33951075366023</v>
+        <v>1.339512850524543</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330191381017968</v>
+        <v>1.330179324394794</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336307325918526</v>
+        <v>1.336299355405806</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338372322626546</v>
+        <v>1.338367184388582</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339154578055914</v>
+        <v>1.339148864235094</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340658124304466</v>
+        <v>1.340656487151529</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340477897352347</v>
+        <v>1.340479332631047</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342670531768289</v>
+        <v>1.34267481774341</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342060963139546</v>
+        <v>1.342065264216677</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343424692619258</v>
+        <v>1.343428843045122</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341765463244178</v>
+        <v>1.341771834062613</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341412529589701</v>
+        <v>1.341417940662966</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343378041291649</v>
+        <v>1.343379938684611</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34700745313002</v>
+        <v>1.347004689825212</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.35050652911211</v>
+        <v>1.350496702128686</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.35195872952933</v>
+        <v>1.351944072693484</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350540544559861</v>
+        <v>1.350524066784392</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349287301802204</v>
+        <v>1.349267742061339</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346113824952884</v>
+        <v>1.346096784432127</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.34473992247614</v>
+        <v>1.344125816049854</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.345867615761168</v>
+        <v>1.345109098050271</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.346749390058719</v>
+        <v>1.345866937024409</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.348064074224525</v>
+        <v>1.347102048623306</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.347670008003989</v>
+        <v>1.346552044057542</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.34726765472291</v>
+        <v>1.345974625578547</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.347037594657167</v>
+        <v>1.345521084946098</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.346869672124757</v>
+        <v>1.34494330348034</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.343245151907867</v>
+        <v>1.340876356136821</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.332666745729547</v>
+        <v>1.329722287324052</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.32595424382128</v>
+        <v>1.322244620520854</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.31551985920037</v>
+        <v>1.310539789995868</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.288674101345932</v>
+        <v>1.282996081228665</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.270940351345932</v>
+        <v>1.258414546169019</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366713126991407</v>
+        <v>1.366714568446806</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359267660601013</v>
+        <v>1.359270305268621</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356335728895337</v>
+        <v>1.356338919397878</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350533334538186</v>
+        <v>1.350537929525323</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348243076630347</v>
+        <v>1.348247869998457</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344075982302098</v>
+        <v>1.344080950780231</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339641890886661</v>
+        <v>1.339646965046864</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337186286795818</v>
+        <v>1.337191410928038</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340041136263745</v>
+        <v>1.340044477492706</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334055855950586</v>
+        <v>1.334055475170496</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334968453475714</v>
+        <v>1.334967994994139</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332790630024333</v>
+        <v>1.332790090326127</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332340733137177</v>
+        <v>1.332338854018623</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329729802409722</v>
+        <v>1.32972824753898</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327908633466332</v>
+        <v>1.327907353827597</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331221630786195</v>
+        <v>1.331220624366671</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329475451225107</v>
+        <v>1.329476381186485</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324388837205058</v>
+        <v>1.324391238628439</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319627781967955</v>
+        <v>1.319631219074036</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319563900005532</v>
+        <v>1.319570293613314</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316704901453052</v>
+        <v>1.316710430280049</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320446028323608</v>
+        <v>1.320450214462405</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318631719358691</v>
+        <v>1.318628793607481</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31290734716482</v>
+        <v>1.312900154186123</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310444376433648</v>
+        <v>1.310433054095022</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303542484115637</v>
+        <v>1.303528609966173</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293695776178084</v>
+        <v>1.293678847945022</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290104919029889</v>
+        <v>1.290085079588175</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294471715366005</v>
+        <v>1.294452167866485</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311000563402632</v>
+        <v>1.310968381723225</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323674621666796</v>
+        <v>1.323640706021495</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355875353037017</v>
+        <v>1.355856809442823</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374602175561074</v>
+        <v>1.374598858518893</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.38033510213804</v>
+        <v>1.380336568558128</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389725497148041</v>
+        <v>1.389732407113305</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391490707520779</v>
+        <v>1.391500607947669</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390079774886169</v>
+        <v>1.390096080456763</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.38981516519831</v>
+        <v>1.389837082227427</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394882336832738</v>
+        <v>1.394920203295637</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391340940498256</v>
+        <v>1.391382115676883</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395136666075087</v>
+        <v>1.395181658833549</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377383521249606</v>
+        <v>1.377417007173963</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372452421787167</v>
+        <v>1.372484611252229</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358738185216154</v>
+        <v>1.358757896675182</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339512850524543</v>
+        <v>1.339514918357592</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330179324394794</v>
+        <v>1.330167484016898</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336299355405806</v>
+        <v>1.336291528036004</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338367184388582</v>
+        <v>1.338362137217606</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339148864235094</v>
+        <v>1.339143249075498</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340656487151529</v>
+        <v>1.34065487439141</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340479332631047</v>
+        <v>1.340480734877727</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34267481774341</v>
+        <v>1.342679020450147</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342065264216677</v>
+        <v>1.342069483187547</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343428843045122</v>
+        <v>1.343432923142556</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341771834062613</v>
+        <v>1.341778093631334</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341417940662966</v>
+        <v>1.341423261107964</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343379938684611</v>
+        <v>1.34338181243191</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347004689825212</v>
+        <v>1.347001986834692</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350496702128686</v>
+        <v>1.35048706434547</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351944072693484</v>
+        <v>1.351929681946021</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350524066784392</v>
+        <v>1.350507861397527</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349267742061339</v>
+        <v>1.349248491345884</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346096784432127</v>
+        <v>1.346079967415035</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.344125816049854</v>
+        <v>1.343537873381309</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.345109098050271</v>
+        <v>1.344412239093975</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.345866937024409</v>
+        <v>1.345050904833938</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.347102048623306</v>
+        <v>1.346186836451915</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.346552044057542</v>
+        <v>1.345520548266611</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.345974625578547</v>
+        <v>1.34479153055069</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.345521084946098</v>
+        <v>1.344136125074803</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.34494330348034</v>
+        <v>1.343180103713583</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.340876356136821</v>
+        <v>1.338711019180651</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.329722287324052</v>
+        <v>1.327049318038184</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.322244620520854</v>
+        <v>1.318935896077514</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.310539789995868</v>
+        <v>1.306304325822678</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.282996081228665</v>
+        <v>1.278693253393726</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.258414546169019</v>
+        <v>1.25334974173016</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.343537873381309</v>
+        <v>1.343623587446217</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.344412239093975</v>
+        <v>1.344510344967725</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.345050904833938</v>
+        <v>1.345155398496744</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.346186836451915</v>
+        <v>1.346300227712531</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.345520548266611</v>
+        <v>1.345646870090485</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.34479153055069</v>
+        <v>1.344931806953228</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.344136125074803</v>
+        <v>1.344289585291528</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.343180103713583</v>
+        <v>1.343355446971137</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.338711019180651</v>
+        <v>1.338914836326347</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.327049318038184</v>
+        <v>1.327295848366671</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.318935896077514</v>
+        <v>1.319242130363806</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.306304325822678</v>
+        <v>1.306735669884045</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.278693253393726</v>
+        <v>1.27938378216271</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.25334974173016</v>
+        <v>1.254862106009994</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366714568446806</v>
+        <v>1.36671598369611</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359270305268621</v>
+        <v>1.359272901939424</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356338919397878</v>
+        <v>1.356342052192167</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350537929525323</v>
+        <v>1.350542441349073</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348247869998457</v>
+        <v>1.348252576592386</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344080950780231</v>
+        <v>1.344085829292451</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339646965046864</v>
+        <v>1.339651947320049</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337191410928038</v>
+        <v>1.337196442276107</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340044477492706</v>
+        <v>1.340047759222226</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334055475170496</v>
+        <v>1.334055101767915</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334967994994139</v>
+        <v>1.334967545314126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332790090326127</v>
+        <v>1.332789560914195</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332338854018623</v>
+        <v>1.332337009653627</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.32972824753898</v>
+        <v>1.32972672125843</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327907353827597</v>
+        <v>1.327906097521572</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331220624366671</v>
+        <v>1.331219636271699</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329476381186485</v>
+        <v>1.329477293583683</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324391238628439</v>
+        <v>1.324393595662364</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319631219074036</v>
+        <v>1.319634592810397</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319570293613314</v>
+        <v>1.319576571476423</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316710430280049</v>
+        <v>1.316715861257457</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320450214462405</v>
+        <v>1.320454328553273</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318628793607481</v>
+        <v>1.318625924169715</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312900154186123</v>
+        <v>1.312893095392161</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310433054095022</v>
+        <v>1.31042194133855</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303528609966173</v>
+        <v>1.3035149916061</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293678847945022</v>
+        <v>1.293662230963203</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290085079588175</v>
+        <v>1.290065603957257</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294452167866485</v>
+        <v>1.294432975985983</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310968381723225</v>
+        <v>1.310936777697947</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323640706021495</v>
+        <v>1.323607399107443</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355856809442823</v>
+        <v>1.355838593822208</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374598858518893</v>
+        <v>1.374595599107628</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380336568558128</v>
+        <v>1.380338003108344</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389732407113305</v>
+        <v>1.389739183340966</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391500607947669</v>
+        <v>1.391510315516278</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390096080456763</v>
+        <v>1.390112076032567</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389837082227427</v>
+        <v>1.389858586396505</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394920203295637</v>
+        <v>1.394957382484084</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391382115676883</v>
+        <v>1.391422547860442</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395181658833549</v>
+        <v>1.395225844414815</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377417007173963</v>
+        <v>1.377449902313584</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372484611252229</v>
+        <v>1.372516238035202</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358757896675182</v>
+        <v>1.35877727282444</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339514918357592</v>
+        <v>1.339516957704831</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330167484016898</v>
+        <v>1.330155854129673</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336291528036004</v>
+        <v>1.336283839996383</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338362137217606</v>
+        <v>1.338357178722825</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339143249075498</v>
+        <v>1.339137730055788</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.34065487439141</v>
+        <v>1.340653285511914</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340480734877727</v>
+        <v>1.340482105171536</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342679020450147</v>
+        <v>1.342683142281448</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342069483187547</v>
+        <v>1.342073622370501</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343432923142556</v>
+        <v>1.343436934663714</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341778093631334</v>
+        <v>1.341784244827387</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341423261107964</v>
+        <v>1.341428493158719</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.34338181243191</v>
+        <v>1.343383662885113</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347001986834692</v>
+        <v>1.346999342282528</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.35048706434547</v>
+        <v>1.350477610423424</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351929681946021</v>
+        <v>1.351915550218778</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350507861397527</v>
+        <v>1.350491921907929</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349248491345884</v>
+        <v>1.34922954271191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346079967415035</v>
+        <v>1.346063370258026</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.343623587446217</v>
+        <v>1.34314245733576</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.344510344967725</v>
+        <v>1.343936808373816</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.345155398496744</v>
+        <v>1.344473880460931</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.346300227712531</v>
+        <v>1.345532629333485</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.345646870090485</v>
+        <v>1.34478259470174</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.344931806953228</v>
+        <v>1.34393935825455</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.344289585291528</v>
+        <v>1.343120707117689</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.343355446971137</v>
+        <v>1.341856317457164</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.338914836326347</v>
+        <v>1.337077151728821</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.327295848366671</v>
+        <v>1.325049010691743</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.319242130363806</v>
+        <v>1.316512639999392</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.306735669884045</v>
+        <v>1.303417130248989</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.27938378216271</v>
+        <v>1.276499394891978</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.254862106009994</v>
+        <v>1.252732459351333</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36671598369611</v>
+        <v>1.366717373447515</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359272901939424</v>
+        <v>1.359275451908206</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356342052192167</v>
+        <v>1.356345128829691</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350542441349073</v>
+        <v>1.350546872246607</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348252576592386</v>
+        <v>1.348257198746984</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344085829292451</v>
+        <v>1.344090620260072</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339651947320049</v>
+        <v>1.339656840179439</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337196442276107</v>
+        <v>1.337201383337187</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340047759222226</v>
+        <v>1.340050983026603</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334055101767915</v>
+        <v>1.334054735531267</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334967545314126</v>
+        <v>1.334967104185313</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332789560914195</v>
+        <v>1.332789041497831</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332337009653627</v>
+        <v>1.332335199087376</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.32972672125843</v>
+        <v>1.329725222787143</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327906097521572</v>
+        <v>1.327904863915983</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331219636271699</v>
+        <v>1.331218666005458</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329477293583683</v>
+        <v>1.329478188908889</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324393595662364</v>
+        <v>1.324395909525347</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319634592810397</v>
+        <v>1.319637904912262</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319576571476423</v>
+        <v>1.319582736708815</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316715861257457</v>
+        <v>1.316721196957005</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320454328553273</v>
+        <v>1.320458372433685</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318625924169715</v>
+        <v>1.318623109441421</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312893095392161</v>
+        <v>1.312886167069087</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31042194133855</v>
+        <v>1.31041103240681</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.3035149916061</v>
+        <v>1.303501622036967</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293662230963203</v>
+        <v>1.293645916740216</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290065603957257</v>
+        <v>1.290046482237668</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294432975985983</v>
+        <v>1.294414130118276</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310936777697947</v>
+        <v>1.310905735927417</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323607399107443</v>
+        <v>1.323574684697823</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355838593822208</v>
+        <v>1.355820697562083</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374595599107628</v>
+        <v>1.374592395846734</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380338003108344</v>
+        <v>1.380339406792934</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389739183340966</v>
+        <v>1.389745829662174</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391510315516278</v>
+        <v>1.3915198357754</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390112076032567</v>
+        <v>1.390127770339085</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389858586396505</v>
+        <v>1.389879689224119</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394957382484084</v>
+        <v>1.394993892915422</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391422547860442</v>
+        <v>1.391462256946651</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395225844414815</v>
+        <v>1.395269244316635</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377449902313584</v>
+        <v>1.377482222138194</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372516238035202</v>
+        <v>1.372547316725385</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35877727282444</v>
+        <v>1.358796322106973</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339516957704831</v>
+        <v>1.339518969100521</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330155854129673</v>
+        <v>1.330144429180482</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336283839996383</v>
+        <v>1.336276287608096</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338357178722825</v>
+        <v>1.338352306596083</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339137730055788</v>
+        <v>1.339132304739361</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340653285511914</v>
+        <v>1.340651720013836</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340482105171536</v>
+        <v>1.340483444546473</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342683142281448</v>
+        <v>1.34268718553979</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342073622370501</v>
+        <v>1.342077683997771</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343436934663714</v>
+        <v>1.343440879303804</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341784244827387</v>
+        <v>1.341790290429866</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341428493158719</v>
+        <v>1.341433638977314</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343383662885113</v>
+        <v>1.343385490393213</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346999342282528</v>
+        <v>1.346996754367563</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350477610423424</v>
+        <v>1.350468335220118</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351915550218778</v>
+        <v>1.351901670687799</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350491921907929</v>
+        <v>1.350476242021005</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34922954271191</v>
+        <v>1.349210889409518</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346063370258026</v>
+        <v>1.346046989362434</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.34314245733576</v>
+        <v>1.342639279800956</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.343936808373816</v>
+        <v>1.343337941611197</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.344473880460931</v>
+        <v>1.343767172525393</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.345532629333485</v>
+        <v>1.344733552123851</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.34478259470174</v>
+        <v>1.343884054217109</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.34393935825455</v>
+        <v>1.342909569286682</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.343120707117689</v>
+        <v>1.341914301452888</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.341856317457164</v>
+        <v>1.340325919027143</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.337077151728821</v>
+        <v>1.335216746414752</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.325049010691743</v>
+        <v>1.322785457991376</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.316512639999392</v>
+        <v>1.313793034409441</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.303417130248989</v>
+        <v>1.300171304321689</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.276499394891978</v>
+        <v>1.273635055795222</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.252732459351333</v>
+        <v>1.250366497950168</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366717373447515</v>
+        <v>1.366718738383928</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359275451908206</v>
+        <v>1.359277956423595</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356345128829691</v>
+        <v>1.35634815080682</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350546872246607</v>
+        <v>1.350551224375574</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348257198746984</v>
+        <v>1.348261738714093</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344090620260072</v>
+        <v>1.344095326018306</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339656840179439</v>
+        <v>1.339661646010301</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337201383337187</v>
+        <v>1.337206236519641</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340050983026603</v>
+        <v>1.340054150425118</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334054735531267</v>
+        <v>1.334054376256966</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334967104185313</v>
+        <v>1.334966671366719</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332789041497831</v>
+        <v>1.332788531797166</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332335199087376</v>
+        <v>1.3323334213997</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329725222787143</v>
+        <v>1.329723751372363</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327904863915983</v>
+        <v>1.327903652401187</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331218666005458</v>
+        <v>1.331217713089851</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329478188908889</v>
+        <v>1.329479067636097</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324395909525347</v>
+        <v>1.324398181391737</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319637904912262</v>
+        <v>1.31964115705212</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319582736708815</v>
+        <v>1.319588792313769</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316721196957005</v>
+        <v>1.316726439861188</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320458372433685</v>
+        <v>1.320462347879408</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318623109441421</v>
+        <v>1.318620347878757</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312886167069087</v>
+        <v>1.312879365638641</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31041103240681</v>
+        <v>1.310400321751061</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303501622036967</v>
+        <v>1.303488494512951</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293645916740216</v>
+        <v>1.293629897089344</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290046482237668</v>
+        <v>1.29002770488529</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294414130118276</v>
+        <v>1.294395620999666</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310905735927417</v>
+        <v>1.310875241554251</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323574684697823</v>
+        <v>1.323542547136914</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355820697562083</v>
+        <v>1.355803112347911</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374592395846734</v>
+        <v>1.374589247305637</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380339406792934</v>
+        <v>1.380340780575111</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389745829662174</v>
+        <v>1.389752349763618</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.3915198357754</v>
+        <v>1.391529174064045</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390127770339085</v>
+        <v>1.39014317177846</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389879689224119</v>
+        <v>1.389900401805603</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394993892915422</v>
+        <v>1.395029752448582</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391462256946651</v>
+        <v>1.391501262130188</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395269244316635</v>
+        <v>1.395311879281149</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377482222138194</v>
+        <v>1.377513981583095</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372547316725385</v>
+        <v>1.372577861413355</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358796322106973</v>
+        <v>1.35881505268622</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339518969100521</v>
+        <v>1.339520953067876</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330144429180482</v>
+        <v>1.330133203809905</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336276287608096</v>
+        <v>1.336268867320381</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338352306596083</v>
+        <v>1.338347518608334</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339132304739361</v>
+        <v>1.339126970770843</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340651720013836</v>
+        <v>1.340650177410618</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340483444546473</v>
+        <v>1.340484753993684</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34268718553979</v>
+        <v>1.342691152441396</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342077683997771</v>
+        <v>1.342081670219426</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343440879303804</v>
+        <v>1.343444758703349</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341790290429866</v>
+        <v>1.341796233124027</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341433638977314</v>
+        <v>1.341438700656717</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343385490393213</v>
+        <v>1.343387295302318</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346996754367563</v>
+        <v>1.346994221359813</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350468335220118</v>
+        <v>1.350459233780855</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351901670687799</v>
+        <v>1.351888036763052</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350476242021005</v>
+        <v>1.350460815631903</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349210889409518</v>
+        <v>1.349192524876732</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346046989362434</v>
+        <v>1.34603082117617</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342639279800956</v>
+        <v>1.342638719153888</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.343337941611197</v>
+        <v>1.342874747690956</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.343767172525393</v>
+        <v>1.343233942717827</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.344733552123851</v>
+        <v>1.344068259835223</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.343884054217109</v>
+        <v>1.34304504566597</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.342909569286682</v>
+        <v>1.342008362317604</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.341914301452888</v>
+        <v>1.340922360352118</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.340325919027143</v>
+        <v>1.339151336020897</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.335216746414752</v>
+        <v>1.33389475202217</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.322785457991376</v>
+        <v>1.32154562753694</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.313793034409441</v>
+        <v>1.312353062640013</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.300171304321689</v>
+        <v>1.298948109951272</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.273635055795222</v>
+        <v>1.27401006236629</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,15 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.250366497950168</v>
+        <v>1.253913390886272</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>1.269538702971715</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366718738383928</v>
+        <v>1.366720079164082</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359277956423595</v>
+        <v>1.359280416690103</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35634815080682</v>
+        <v>1.356351119567238</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350551224375574</v>
+        <v>1.35055549981761</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348261738714093</v>
+        <v>1.3482661986662</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344095326018306</v>
+        <v>1.344099948820054</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339661646010301</v>
+        <v>1.339666367113818</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337206236519641</v>
+        <v>1.33721100414694</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340054150425118</v>
+        <v>1.340057262884413</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334054376256966</v>
+        <v>1.334054023749039</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334966671366719</v>
+        <v>1.334966246626316</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332788531797166</v>
+        <v>1.332788031542659</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.3323334213997</v>
+        <v>1.332331675703514</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329723751372363</v>
+        <v>1.329722306288242</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327903652401187</v>
+        <v>1.327902462389177</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331217713089851</v>
+        <v>1.331216777063719</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329479067636097</v>
+        <v>1.329479930221941</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324398181391737</v>
+        <v>1.324400412393708</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.31964115705212</v>
+        <v>1.319644350842532</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319588792313769</v>
+        <v>1.319594741188757</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316726439861188</v>
+        <v>1.31673159236711</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320462347879408</v>
+        <v>1.320466256607054</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318620347878757</v>
+        <v>1.318617637995227</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312879365638641</v>
+        <v>1.312872687652021</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310400321751061</v>
+        <v>1.310389804021884</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303488494512951</v>
+        <v>1.303475602529578</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293629897089344</v>
+        <v>1.293614164115954</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.29002770488529</v>
+        <v>1.290009262695575</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294395620999666</v>
+        <v>1.294377439693864</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310875241554251</v>
+        <v>1.310845280239456</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323542547136914</v>
+        <v>1.323510971315211</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355803112347911</v>
+        <v>1.355785830150903</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374589247305637</v>
+        <v>1.374586152101648</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380340780575111</v>
+        <v>1.380342125379098</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389752349763618</v>
+        <v>1.389758747194244</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391529174064045</v>
+        <v>1.391538335521215</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.39014317177846</v>
+        <v>1.390158288444269</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389900401805603</v>
+        <v>1.389920734832256</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395029752448582</v>
+        <v>1.395064978313052</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391501262130188</v>
+        <v>1.391539581933419</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395311879281149</v>
+        <v>1.395353769327744</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377513981583095</v>
+        <v>1.377545195072004</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372577861413355</v>
+        <v>1.372607885712034</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35881505268622</v>
+        <v>1.358833472457423</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339520953067876</v>
+        <v>1.339522910119209</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330133203809905</v>
+        <v>1.330122172843415</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336268867320381</v>
+        <v>1.336261575705044</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338347518608334</v>
+        <v>1.338342812606298</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339126970770843</v>
+        <v>1.339121725872749</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340650177410618</v>
+        <v>1.34064865722802</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340484753993684</v>
+        <v>1.340486034463604</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342691152441396</v>
+        <v>1.342695045120228</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342081670219426</v>
+        <v>1.342085583107098</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343444758703349</v>
+        <v>1.343448574450337</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341796233124027</v>
+        <v>1.341802075505204</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341438700656717</v>
+        <v>1.341443680223488</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343387295302318</v>
+        <v>1.343389077955375</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346994221359813</v>
+        <v>1.346991741597058</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350459233780855</v>
+        <v>1.350450301330278</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351888036763052</v>
+        <v>1.351874642078647</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350460815631903</v>
+        <v>1.350445636818758</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349192524876732</v>
+        <v>1.349174442733576</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.34603082117617</v>
+        <v>1.346014862195102</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342638719153888</v>
+        <v>1.342638073666135</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.342874747690956</v>
+        <v>1.342527107372269</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.343233942717827</v>
+        <v>1.342823122616169</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.344068259835223</v>
+        <v>1.343532058580575</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.34304504566597</v>
+        <v>1.342356223471237</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.342008362317604</v>
+        <v>1.341276853490214</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.340922360352118</v>
+        <v>1.34013016837385</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.339151336020897</v>
+        <v>1.338214441921617</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.33389475202217</v>
+        <v>1.33286990650891</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.32154562753694</v>
+        <v>1.32065237419192</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.312353062640013</v>
+        <v>1.311383292069884</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.298948109951272</v>
+        <v>1.298332947107752</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.27401006236629</v>
+        <v>1.275050633161382</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.253913390886272</v>
+        <v>1.257728135410571</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.269538702971715</v>
+        <v>1.274282663304243</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.342527107372269</v>
+        <v>1.342412164147452</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.342823122616169</v>
+        <v>1.342708866982444</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.343532058580575</v>
+        <v>1.343412498664932</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.342356223471237</v>
+        <v>1.342299337191393</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.341276853490214</v>
+        <v>1.341176402097375</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.34013016837385</v>
+        <v>1.339976216590639</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.338214441921617</v>
+        <v>1.33802292750909</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.33286990650891</v>
+        <v>1.332610327077153</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.32065237419192</v>
+        <v>1.320342808677571</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.311383292069884</v>
+        <v>1.310946710893212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.298332947107752</v>
+        <v>1.297745584485779</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.275050633161382</v>
+        <v>1.274119601062309</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.257728135410571</v>
+        <v>1.256260421004634</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.274282663304243</v>
+        <v>1.268109210244422</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366720079164082</v>
+        <v>1.366721396423604</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359280416690103</v>
+        <v>1.35928283387006</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356351119567238</v>
+        <v>1.356354036504235</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.35055549981761</v>
+        <v>1.350559700581651</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.3482661986662</v>
+        <v>1.3482705806999</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344099948820054</v>
+        <v>1.344104490839497</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339666367113818</v>
+        <v>1.33967100571076</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.33721100414694</v>
+        <v>1.337215688461371</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340057262884413</v>
+        <v>1.34006032182075</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334054023749039</v>
+        <v>1.334053677818781</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334966246626316</v>
+        <v>1.334965829740612</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332788031542659</v>
+        <v>1.332787540474634</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332331675703514</v>
+        <v>1.332329961143347</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329722306288242</v>
+        <v>1.329720886834653</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327902462389177</v>
+        <v>1.327901293312625</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331216777063719</v>
+        <v>1.331215857482097</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329479930221941</v>
+        <v>1.329480777106477</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324400412393708</v>
+        <v>1.324402603623132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319644350842532</v>
+        <v>1.31964748783879</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319594741188757</v>
+        <v>1.319600586130061</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31673159236711</v>
+        <v>1.316736656790115</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320466256607054</v>
+        <v>1.320470100276516</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318617637995227</v>
+        <v>1.318614978359057</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312872687652021</v>
+        <v>1.312866129784096</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310389804021884</v>
+        <v>1.310379474060323</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303475602529578</v>
+        <v>1.303462939813038</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293614164115954</v>
+        <v>1.293598710204604</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290009262695575</v>
+        <v>1.2899911467886</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294377439693864</v>
+        <v>1.294359577577669</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310845280239456</v>
+        <v>1.310815838140034</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323510971315211</v>
+        <v>1.323479942645832</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355785830150903</v>
+        <v>1.355768843215864</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374586152101648</v>
+        <v>1.374583108898</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380342125379098</v>
+        <v>1.380343442092059</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389758747194244</v>
+        <v>1.389765025371616</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391538335521215</v>
+        <v>1.391547325095144</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390158288444269</v>
+        <v>1.390173128135518</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389920734832256</v>
+        <v>1.389940698609517</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395064978313052</v>
+        <v>1.395099587136326</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391539581933419</v>
+        <v>1.39157723423553</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395353769327744</v>
+        <v>1.39539493378422</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377545195072004</v>
+        <v>1.377575876538732</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372607885712034</v>
+        <v>1.372637402776703</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358833472457423</v>
+        <v>1.358851589058489</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339522910119209</v>
+        <v>1.339524840756094</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330122172843415</v>
+        <v>1.330111331283492</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336261575705044</v>
+        <v>1.33625440945123</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338342812606298</v>
+        <v>1.338338186509278</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339121725872749</v>
+        <v>1.339116567842308</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.34064865722802</v>
+        <v>1.340647159003789</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340486034463604</v>
+        <v>1.340487286867987</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342695045120228</v>
+        <v>1.342698865631749</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342085583107098</v>
+        <v>1.34208942465752</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343448574450337</v>
+        <v>1.343452328082273</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341802075505204</v>
+        <v>1.341807820082523</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341443680223488</v>
+        <v>1.341448579640355</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343389077955375</v>
+        <v>1.343390838691934</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346991741597058</v>
+        <v>1.346989313481635</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350450301330278</v>
+        <v>1.350441533264418</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351874642078647</v>
+        <v>1.351861480483541</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350445636818758</v>
+        <v>1.350430699836228</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349174442733576</v>
+        <v>1.349156636776353</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346014862195102</v>
+        <v>1.345999108964205</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342638073666135</v>
+        <v>1.342637347863076</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.342412164147452</v>
+        <v>1.341878555594685</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.342708866982444</v>
+        <v>1.342103568907349</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.343412498664932</v>
+        <v>1.342680056280589</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.342299337191393</v>
+        <v>1.341473132922757</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.341176402097375</v>
+        <v>1.340252898717284</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.339976216590639</v>
+        <v>1.3389294818484</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.33802292750909</v>
+        <v>1.336786211685451</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.332610327077153</v>
+        <v>1.33120277123228</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.320342808677571</v>
+        <v>1.318982623152689</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.310946710893212</v>
+        <v>1.309351006101209</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.297745584485779</v>
+        <v>1.296260058483603</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.274119601062309</v>
+        <v>1.273627138237867</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.256260421004634</v>
+        <v>1.257164918649567</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.268109210244422</v>
+        <v>1.264881529012712</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366721396423604</v>
+        <v>1.366722690776012</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35928283387006</v>
+        <v>1.359285209085441</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356354036504235</v>
+        <v>1.356356902962889</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350559700581651</v>
+        <v>1.350563828607077</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.3482705806999</v>
+        <v>1.348274886839189</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344104490839497</v>
+        <v>1.34410895417551</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33967100571076</v>
+        <v>1.339675563944972</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337215688461371</v>
+        <v>1.337220291627556</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.34006032182075</v>
+        <v>1.340063328602159</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334053677818781</v>
+        <v>1.334053338284415</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334965829740612</v>
+        <v>1.334965420494264</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332787540474634</v>
+        <v>1.332787058342828</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332329961143347</v>
+        <v>1.332328276893943</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329720886834653</v>
+        <v>1.329719492336059</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327901293312625</v>
+        <v>1.327900144623985</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331215857482097</v>
+        <v>1.331214953915511</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329480777106477</v>
+        <v>1.329481608713933</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324402603623132</v>
+        <v>1.324404756133353</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.31964748783879</v>
+        <v>1.319650569541435</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319600586130061</v>
+        <v>1.319606329837155</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316736656790115</v>
+        <v>1.316741635367237</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320470100276516</v>
+        <v>1.320473880493282</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318614978359057</v>
+        <v>1.3186123675907</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312866129784096</v>
+        <v>1.312859688827917</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310379474060323</v>
+        <v>1.310369326889492</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303462939813038</v>
+        <v>1.303450500310064</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293598710204604</v>
+        <v>1.293583528006828</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.2899911467886</v>
+        <v>1.289973348594905</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294359577577669</v>
+        <v>1.294342026327391</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310815838140034</v>
+        <v>1.310786901887743</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323479942645832</v>
+        <v>1.323449447042136</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355768843215864</v>
+        <v>1.355752144049652</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374583108898</v>
+        <v>1.374580116401966</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380343442092059</v>
+        <v>1.38034473156591</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389765025371616</v>
+        <v>1.389771187587918</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391547325095144</v>
+        <v>1.391556147552028</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390173128135518</v>
+        <v>1.390187698369885</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389940698609517</v>
+        <v>1.389960303074168</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395099587136326</v>
+        <v>1.395133594969938</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.39157723423553</v>
+        <v>1.391614236300162</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.39539493378422</v>
+        <v>1.395435391316358</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377575876538732</v>
+        <v>1.377606039447764</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372637402776703</v>
+        <v>1.372666425324026</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358851589058489</v>
+        <v>1.358869409880331</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339524840756094</v>
+        <v>1.339526745469534</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330111331283492</v>
+        <v>1.330100674302134</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33625440945123</v>
+        <v>1.336247365360455</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338338186509278</v>
+        <v>1.338333638306142</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339116567842308</v>
+        <v>1.339111494548444</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340647159003789</v>
+        <v>1.340645682287341</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340487286867987</v>
+        <v>1.340488512081814</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342698865631749</v>
+        <v>1.342702615956495</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34208942465752</v>
+        <v>1.342093196795863</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343452328082273</v>
+        <v>1.343456021088146</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341807820082523</v>
+        <v>1.34181346928244</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341448579640355</v>
+        <v>1.341453400808672</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343390838691934</v>
+        <v>1.343392577847936</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346989313481635</v>
+        <v>1.346986935477393</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350441533264418</v>
+        <v>1.350432925143146</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351861480483541</v>
+        <v>1.351848546032685</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350430699836228</v>
+        <v>1.350415999109263</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349156636776353</v>
+        <v>1.349139100972087</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345999108964205</v>
+        <v>1.345983558078491</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342637347863076</v>
+        <v>1.342636546041889</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.341878555594685</v>
+        <v>1.341365898200593</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.342103568907349</v>
+        <v>1.341523037839271</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.342680056280589</v>
+        <v>1.34197621194196</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.341473132922757</v>
+        <v>1.340681699358918</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.340252898717284</v>
+        <v>1.339368747458926</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.3389294818484</v>
+        <v>1.337929052500337</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.336786211685451</v>
+        <v>1.33560900568319</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.33120277123228</v>
+        <v>1.329870843061849</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.318982623152689</v>
+        <v>1.317705713386157</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.309351006101209</v>
+        <v>1.30787112539447</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.296260058483603</v>
+        <v>1.294913205759118</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.273627138237867</v>
+        <v>1.273190246735791</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.257164918649567</v>
+        <v>1.257869325140208</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.264881529012712</v>
+        <v>1.263223279670845</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366722690776012</v>
+        <v>1.366723962813672</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359285209085441</v>
+        <v>1.359287543419602</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356356902962889</v>
+        <v>1.356359720242134</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350563828607077</v>
+        <v>1.350567885766703</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348274886839189</v>
+        <v>1.348279119038569</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.34410895417551</v>
+        <v>1.344113340854889</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339675563944972</v>
+        <v>1.339680043886668</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337220291627556</v>
+        <v>1.337224815735779</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340063328602159</v>
+        <v>1.340066284550469</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334053338284415</v>
+        <v>1.334053004970781</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334965420494264</v>
+        <v>1.334965018679716</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332787058342828</v>
+        <v>1.332786584905971</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332328276893943</v>
+        <v>1.332326622158945</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329719492336059</v>
+        <v>1.329718122140445</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327900144623985</v>
+        <v>1.327899015794636</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331214953915511</v>
+        <v>1.331214065949312</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329481608713933</v>
+        <v>1.329482425453409</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324404756133353</v>
+        <v>1.32440687094087</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319650569541435</v>
+        <v>1.319653597398641</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319606329837155</v>
+        <v>1.319611974916852</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316741635367237</v>
+        <v>1.316746530260482</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320473880493282</v>
+        <v>1.320477598810637</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.3186123675907</v>
+        <v>1.318609804360488</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312859688827917</v>
+        <v>1.312853361689519</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310369326889492</v>
+        <v>1.310359357706627</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303450500310064</v>
+        <v>1.303438278178342</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293583528006828</v>
+        <v>1.293568610429552</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.289973348594905</v>
+        <v>1.289955859842057</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294342026327391</v>
+        <v>1.294324777905967</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310786901887743</v>
+        <v>1.310758458568937</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323449447042136</v>
+        <v>1.323419470896482</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355752144049652</v>
+        <v>1.355735725410222</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374580116401966</v>
+        <v>1.37457717336307</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.38034473156591</v>
+        <v>1.380345994619031</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389771187587918</v>
+        <v>1.389777237015636</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391556147552028</v>
+        <v>1.391564807484289</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390187698369885</v>
+        <v>1.390202006396254</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389960303074168</v>
+        <v>1.389979557810634</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395133594969938</v>
+        <v>1.395167017314153</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391614236300162</v>
+        <v>1.391650604801631</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395435391316358</v>
+        <v>1.395475159955987</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377606039447764</v>
+        <v>1.377635696813827</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372666425324026</v>
+        <v>1.372694965650129</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358869409880331</v>
+        <v>1.358886942076718</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339526745469534</v>
+        <v>1.33952862474013</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330100674302134</v>
+        <v>1.330090197233745</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336247365360455</v>
+        <v>1.336240440341891</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338333638306142</v>
+        <v>1.338329166052449</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339111494548444</v>
+        <v>1.339106503928893</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340645682287341</v>
+        <v>1.340644226639447</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340488512081814</v>
+        <v>1.340489710945085</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342702615956495</v>
+        <v>1.342706298003443</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342093196795863</v>
+        <v>1.342096901378905</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343456021088146</v>
+        <v>1.343459654910293</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34181346928244</v>
+        <v>1.341819025452102</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341453400808672</v>
+        <v>1.341458145570773</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343392577847936</v>
+        <v>1.343394295755531</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346986935477393</v>
+        <v>1.346984606106834</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350432925143146</v>
+        <v>1.350424472683035</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351848546032685</v>
+        <v>1.351835832978607</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350415999109263</v>
+        <v>1.35040152922713</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349139100972087</v>
+        <v>1.34912182945316</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345983558078491</v>
+        <v>1.345968206183743</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342636546041889</v>
+        <v>1.342635672283987</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.341365898200593</v>
+        <v>1.340960241647184</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.341523037839271</v>
+        <v>1.341067499309273</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.34197621194196</v>
+        <v>1.341402897700629</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.340681699358918</v>
+        <v>1.340039192541445</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.339368747458926</v>
+        <v>1.338657050763321</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.337929052500337</v>
+        <v>1.337125398106183</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.33560900568319</v>
+        <v>1.334663742993768</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.329870843061849</v>
+        <v>1.32881701901342</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.317705713386157</v>
+        <v>1.316753997944182</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.30787112539447</v>
+        <v>1.306811389203784</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.294913205759118</v>
+        <v>1.294106494928385</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.273190246735791</v>
+        <v>1.273383482899491</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.257869325140208</v>
+        <v>1.259289754306874</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.263223279670845</v>
+        <v>1.264093564059924</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366723962813672</v>
+        <v>1.366725213108701</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359287543419602</v>
+        <v>1.359289837918929</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356359720242134</v>
+        <v>1.356362489596721</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350567885766703</v>
+        <v>1.350571873869602</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348279119038569</v>
+        <v>1.34828327918601</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344113340854889</v>
+        <v>1.344117652835421</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339680043886668</v>
+        <v>1.339684447535571</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337224815735779</v>
+        <v>1.337229262805153</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340066284550469</v>
+        <v>1.340069190943239</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334053004970781</v>
+        <v>1.334052677709039</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334965018679716</v>
+        <v>1.334964624096841</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332786584905971</v>
+        <v>1.332786119931387</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332326622158945</v>
+        <v>1.332324996169637</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329718122140445</v>
+        <v>1.329716775618301</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327899015794636</v>
+        <v>1.327897906314072</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331214065949312</v>
+        <v>1.331213193183035</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329482425453409</v>
+        <v>1.329483227719547</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32440687094087</v>
+        <v>1.324408949026938</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319653597398641</v>
+        <v>1.319656572808485</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319611974916852</v>
+        <v>1.319617523887248</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316746530260482</v>
+        <v>1.316751343559944</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320477598810637</v>
+        <v>1.320481256731755</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318609804360488</v>
+        <v>1.318607287386403</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312853361689519</v>
+        <v>1.312847145382998</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310359357706627</v>
+        <v>1.310349561875544</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303438278178342</v>
+        <v>1.303426267777404</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293568610429552</v>
+        <v>1.293553950624116</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.289955859842057</v>
+        <v>1.289938672541919</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294324777905967</v>
+        <v>1.294307824550747</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310758458568937</v>
+        <v>1.310730495705419</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323419470896482</v>
+        <v>1.323390001060059</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355735725410222</v>
+        <v>1.3557195802962</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37457717336307</v>
+        <v>1.374574278571389</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380345994619031</v>
+        <v>1.38034723203788</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389777237015636</v>
+        <v>1.389783176712932</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391564807484289</v>
+        <v>1.391573309318387</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390202006396254</v>
+        <v>1.390216059206591</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389979557810634</v>
+        <v>1.389998472066417</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395167017314153</v>
+        <v>1.395199869141405</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391650604801631</v>
+        <v>1.391686355849827</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395475159955987</v>
+        <v>1.395514257127632</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377635696813827</v>
+        <v>1.37766486122047</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372694965650129</v>
+        <v>1.372723035647797</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358886942076718</v>
+        <v>1.358904192573656</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33952862474013</v>
+        <v>1.339530479038266</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330090197233745</v>
+        <v>1.330079895568371</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336240440341891</v>
+        <v>1.336233631407882</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338329166052449</v>
+        <v>1.338324767867718</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339106503928893</v>
+        <v>1.339101593987465</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340644226639447</v>
+        <v>1.340642791631921</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340489710945085</v>
+        <v>1.340490884264523</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342706298003443</v>
+        <v>1.342709913613204</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342096901378905</v>
+        <v>1.342100540198029</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343459654910293</v>
+        <v>1.34346323094619</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341819025452102</v>
+        <v>1.341824490862553</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341458145570773</v>
+        <v>1.341462815712216</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343394295755531</v>
+        <v>1.343395992742928</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346984606106834</v>
+        <v>1.346982323948389</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350424472683035</v>
+        <v>1.350416171750569</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351835832978607</v>
+        <v>1.351823335763392</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.35040152922713</v>
+        <v>1.350387284937668</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34912182945316</v>
+        <v>1.34910481651211</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345968206183743</v>
+        <v>1.345953049977076</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342635672283987</v>
+        <v>1.342634730466704</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340960241647184</v>
+        <v>1.340570018174727</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.341067499309273</v>
+        <v>1.340631848743155</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.341402897700629</v>
+        <v>1.340850864289878</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.340039192541445</v>
+        <v>1.339424351500962</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.338657050763321</v>
+        <v>1.337975442832056</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.337125398106183</v>
+        <v>1.336356652324578</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.334663742993768</v>
+        <v>1.333762704569069</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.32881701901342</v>
+        <v>1.327817734733205</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.316753997944182</v>
+        <v>1.31585779758201</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.306811389203784</v>
+        <v>1.305823947229112</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.294106494928385</v>
+        <v>1.293368108451113</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.273383482899491</v>
+        <v>1.273547042886269</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.259289754306874</v>
+        <v>1.260461270517622</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.264093564059924</v>
+        <v>1.264653357132961</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366725213108701</v>
+        <v>1.366726442213823</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359289837918929</v>
+        <v>1.359292093594404</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356362489596721</v>
+        <v>1.356365212239083</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350571873869602</v>
+        <v>1.3505757946638</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.34828327918601</v>
+        <v>1.348287369105756</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344117652835421</v>
+        <v>1.344121892008794</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339684447535571</v>
+        <v>1.339688776823883</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337229262805153</v>
+        <v>1.337233634786625</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340069190943239</v>
+        <v>1.340072049015601</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334052677709039</v>
+        <v>1.334052356336385</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334964624096841</v>
+        <v>1.334964236552623</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332786119931387</v>
+        <v>1.332785663194614</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332324996169637</v>
+        <v>1.332323398183759</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329716775618301</v>
+        <v>1.329715452161665</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327897906314072</v>
+        <v>1.327896815689132</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331213193183035</v>
+        <v>1.331212335229805</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329483227719547</v>
+        <v>1.329484015893164</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324408949026938</v>
+        <v>1.324410991339076</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319656572808485</v>
+        <v>1.319659497121087</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319617523887248</v>
+        <v>1.319622979181464</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316751343559944</v>
+        <v>1.316756077286765</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320481256731755</v>
+        <v>1.320484855711702</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318607287386403</v>
+        <v>1.318604815431966</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312847145382998</v>
+        <v>1.312841037025838</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310349561875544</v>
+        <v>1.310339934919489</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303426267777404</v>
+        <v>1.303414463660006</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293553950624116</v>
+        <v>1.293539541975841</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.289938672541919</v>
+        <v>1.289921778978549</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294307824550747</v>
+        <v>1.294291158761888</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310730495705419</v>
+        <v>1.310703001236262</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323390001060059</v>
+        <v>1.323361024823727</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.3557195802962</v>
+        <v>1.355703701936993</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374574278571389</v>
+        <v>1.374571430855929</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.38034723203788</v>
+        <v>1.380348444578512</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389783176712932</v>
+        <v>1.389789009628737</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391573309318387</v>
+        <v>1.391581657322222</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390216059206591</v>
+        <v>1.390229863547193</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389998472066417</v>
+        <v>1.390017054766739</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395199869141405</v>
+        <v>1.395232164918544</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391686355849827</v>
+        <v>1.391721505013858</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395514257127632</v>
+        <v>1.39555269967384</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.37766486122047</v>
+        <v>1.377693544837753</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372723035647797</v>
+        <v>1.372750646822839</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358904192573656</v>
+        <v>1.358921168078336</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339530479038266</v>
+        <v>1.339532308824285</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330079895568371</v>
+        <v>1.330069764945283</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336233631407882</v>
+        <v>1.336226935669689</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338324767867718</v>
+        <v>1.338320441932832</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339101593987465</v>
+        <v>1.339096762791431</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340642791631921</v>
+        <v>1.340641376847322</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340490884264523</v>
+        <v>1.340492032815163</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342709913613204</v>
+        <v>1.342713464561049</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342100540198029</v>
+        <v>1.34210411498207</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34346323094619</v>
+        <v>1.343466750550157</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341824490862553</v>
+        <v>1.341829867711778</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341462815712216</v>
+        <v>1.341467412963921</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343395992742928</v>
+        <v>1.343397669134259</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346982323948389</v>
+        <v>1.346980087633863</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350416171750569</v>
+        <v>1.350408018355716</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351823335763392</v>
+        <v>1.351811049011043</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350387284937668</v>
+        <v>1.350373261141765</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34910481651211</v>
+        <v>1.349088056596607</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345953049977076</v>
+        <v>1.345938086207334</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342634730466704</v>
+        <v>1.342633724274296</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340570018174727</v>
+        <v>1.340583581415612</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.340631848743155</v>
+        <v>1.340325263804826</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.340850864289878</v>
+        <v>1.340513764038604</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.339424351500962</v>
+        <v>1.339073590353521</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.337975442832056</v>
+        <v>1.33744125367932</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.336356652324578</v>
+        <v>1.335763680262203</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.333762704569069</v>
+        <v>1.333050786166352</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.327817734733205</v>
+        <v>1.327032426658264</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.31585779758201</v>
+        <v>1.315188957394275</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.305823947229112</v>
+        <v>1.305267060788782</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.293368108451113</v>
+        <v>1.292959701389609</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.273547042886269</v>
+        <v>1.274080874386307</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.260461270517622</v>
+        <v>1.262075555811492</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,15 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.264653357132961</v>
+        <v>1.266341792177359</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B120">
+        <v>1.271737672727624</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.340513764038604</v>
+        <v>1.340515679433405</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.339073590353521</v>
+        <v>1.339081291902092</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.33744125367932</v>
+        <v>1.337499307781182</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.335763680262203</v>
+        <v>1.335817641154728</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.333050786166352</v>
+        <v>1.33309183320445</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.327032426658264</v>
+        <v>1.327064018733742</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.315188957394275</v>
+        <v>1.315213825434267</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.305267060788782</v>
+        <v>1.305287510410255</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.292959701389609</v>
+        <v>1.292982252568577</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.274080874386307</v>
+        <v>1.274103606182701</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.262075555811492</v>
+        <v>1.262101158033092</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.266341792177359</v>
+        <v>1.26638108872451</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.271737672727624</v>
+        <v>1.271972211861508</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366726442213823</v>
+        <v>1.366727650663188</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359292093594404</v>
+        <v>1.359294311423082</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356365212239083</v>
+        <v>1.356367889341099</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.3505757946638</v>
+        <v>1.350579649838827</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348287369105756</v>
+        <v>1.348291390560992</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344121892008794</v>
+        <v>1.344126060203366</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339688776823883</v>
+        <v>1.339693033619116</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337233634786625</v>
+        <v>1.337237933565824</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340072049015601</v>
+        <v>1.340074859961999</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334052356336385</v>
+        <v>1.334052040695788</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334964236552623</v>
+        <v>1.334963855860837</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332785663194614</v>
+        <v>1.332785214479047</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332323398183759</v>
+        <v>1.332321827484373</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329715452161665</v>
+        <v>1.329714151183201</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327896815689132</v>
+        <v>1.32789574344327</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331212335229805</v>
+        <v>1.331211491715762</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329484015893164</v>
+        <v>1.329484790341848</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324410991339076</v>
+        <v>1.324412998792504</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319659497121087</v>
+        <v>1.319662371640648</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319622979181464</v>
+        <v>1.319628343151195</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316756077286765</v>
+        <v>1.316760733395952</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320484855711702</v>
+        <v>1.320488397159334</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318604815431966</v>
+        <v>1.318602387304244</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312841037025838</v>
+        <v>1.312835033834483</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310339934919489</v>
+        <v>1.31033047251435</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303414463660006</v>
+        <v>1.303402860563931</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293539541975841</v>
+        <v>1.293525378094143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.289921778978549</v>
+        <v>1.289905171696729</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294291158761888</v>
+        <v>1.294274773291339</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310703001236262</v>
+        <v>1.310675963500524</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323361024823727</v>
+        <v>1.323332529899808</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355703701936993</v>
+        <v>1.355688083783359</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374571430855929</v>
+        <v>1.374568629083088</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380348444578512</v>
+        <v>1.380349632968017</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389789009628737</v>
+        <v>1.389794738607568</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391581657322222</v>
+        <v>1.39158985561214</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390229863547193</v>
+        <v>1.390243425929356</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.390017054766739</v>
+        <v>1.390035314528421</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395232164918544</v>
+        <v>1.395263918627977</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391721505013858</v>
+        <v>1.391756067344518</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.39555269967384</v>
+        <v>1.39559050387924</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377693544837753</v>
+        <v>1.377721759439052</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372750646822839</v>
+        <v>1.372777810309658</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358921168078336</v>
+        <v>1.358937875087665</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339532308824285</v>
+        <v>1.339534114548674</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330069764945283</v>
+        <v>1.330059801146857</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336226935669689</v>
+        <v>1.336220350333432</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338320441932832</v>
+        <v>1.33831618648756</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339096762791431</v>
+        <v>1.339092008469037</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340641376847322</v>
+        <v>1.340639981878659</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340492032815163</v>
+        <v>1.340493157341867</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342713464561049</v>
+        <v>1.34271695255977</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34210411498207</v>
+        <v>1.342107627400009</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343466750550157</v>
+        <v>1.343470215034992</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341829867711778</v>
+        <v>1.341835158127609</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341467412963921</v>
+        <v>1.341471939004226</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343397669134259</v>
+        <v>1.343399325249468</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346980087633863</v>
+        <v>1.346977895845998</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350408018355716</v>
+        <v>1.350400008645811</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351811049011043</v>
+        <v>1.351798967520204</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350373261141765</v>
+        <v>1.350359452888057</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349088056596607</v>
+        <v>1.349071544304592</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345938086207334</v>
+        <v>1.345923311675356</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342633724274296</v>
+        <v>1.342632657208278</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340583581415612</v>
+        <v>1.340596846135708</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.340325263804826</v>
+        <v>1.339860323039305</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.340515679433405</v>
+        <v>1.340005047414422</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.339081291902092</v>
+        <v>1.338535402201849</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.337499307781182</v>
+        <v>1.336773705885372</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.335817641154728</v>
+        <v>1.335026932976916</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.33309183320445</v>
+        <v>1.332130299354979</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.327064018733742</v>
+        <v>1.325988334637199</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.315213825434267</v>
+        <v>1.314171217211367</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.305287510410255</v>
+        <v>1.304283695257608</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.292982252568577</v>
+        <v>1.291941910799032</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.274103606182701</v>
+        <v>1.273737094143412</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.262101158033092</v>
+        <v>1.26227285948693</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.26638108872451</v>
+        <v>1.26565840132439</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.271972211861508</v>
+        <v>1.263697779458376</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366727650663188</v>
+        <v>1.36671598369611</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359294311423082</v>
+        <v>1.359272901939424</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356367889341099</v>
+        <v>1.356342052192167</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350579649838827</v>
+        <v>1.350542441349073</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348291390560992</v>
+        <v>1.348252576592386</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344126060203366</v>
+        <v>1.344085829292451</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339693033619116</v>
+        <v>1.339651947320049</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337237933565824</v>
+        <v>1.337196442276107</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340074859961999</v>
+        <v>1.340047759222226</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334052040695788</v>
+        <v>1.334055101767915</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334963855860837</v>
+        <v>1.334967545314126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332785214479047</v>
+        <v>1.332789560914195</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332321827484373</v>
+        <v>1.332337009653627</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329714151183201</v>
+        <v>1.32972672125843</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.32789574344327</v>
+        <v>1.327906097521572</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331211491715762</v>
+        <v>1.331219636271699</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329484790341848</v>
+        <v>1.329477293583683</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324412998792504</v>
+        <v>1.324393595662364</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319662371640648</v>
+        <v>1.319634592810397</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319628343151195</v>
+        <v>1.319576571476423</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316760733395952</v>
+        <v>1.316715861257457</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320488397159334</v>
+        <v>1.320454328553273</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318602387304244</v>
+        <v>1.318625924169715</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312835033834483</v>
+        <v>1.312893095392161</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31033047251435</v>
+        <v>1.31042194133855</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303402860563931</v>
+        <v>1.3035149916061</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293525378094143</v>
+        <v>1.293662230963203</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.289905171696729</v>
+        <v>1.290065603957257</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294274773291339</v>
+        <v>1.294432975985983</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310675963500524</v>
+        <v>1.310936777697947</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323332529899808</v>
+        <v>1.323607399107443</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355688083783359</v>
+        <v>1.355838593822208</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374568629083088</v>
+        <v>1.374595599107628</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380349632968017</v>
+        <v>1.380338003108344</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389794738607568</v>
+        <v>1.389739183340966</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39158985561214</v>
+        <v>1.391510315516278</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390243425929356</v>
+        <v>1.390112076032567</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.390035314528421</v>
+        <v>1.389858586396505</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395263918627977</v>
+        <v>1.394957382484084</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391756067344518</v>
+        <v>1.391422547860442</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.39559050387924</v>
+        <v>1.395225844414815</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377721759439052</v>
+        <v>1.377449902313584</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372777810309658</v>
+        <v>1.372516238035202</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358937875087665</v>
+        <v>1.35877727282444</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339534114548674</v>
+        <v>1.339516957704831</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330059801146857</v>
+        <v>1.330155854129673</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336220350333432</v>
+        <v>1.336283839996383</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.33831618648756</v>
+        <v>1.338357178722825</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339092008469037</v>
+        <v>1.339137730055788</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340639981878659</v>
+        <v>1.340653285511914</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340493157341867</v>
+        <v>1.340482105171536</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34271695255977</v>
+        <v>1.342683142281448</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342107627400009</v>
+        <v>1.342073622370501</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343470215034992</v>
+        <v>1.343436934663714</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341835158127609</v>
+        <v>1.342673152515528</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341471939004226</v>
+        <v>1.341855607602509</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343399325249468</v>
+        <v>1.343645277505046</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346977895845998</v>
+        <v>1.346804215541844</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350400008645811</v>
+        <v>1.350237201810745</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351798967520204</v>
+        <v>1.351426422521746</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350359452888057</v>
+        <v>1.349565853059778</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349071544304592</v>
+        <v>1.3480690811753</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345923311675356</v>
+        <v>1.345378743734077</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342632657208278</v>
+        <v>1.342563290323664</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340596846135708</v>
+        <v>1.340286356850262</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.339860323039305</v>
+        <v>1.33853837782645</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.340005047414422</v>
+        <v>1.338799637087031</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.338535402201849</v>
+        <v>1.336892023981409</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.336773705885372</v>
+        <v>1.335701655887481</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.335026932976916</v>
+        <v>1.333497490712664</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.332130299354979</v>
+        <v>1.331196495258095</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.325988334637199</v>
+        <v>1.326522058394633</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.314171217211367</v>
+        <v>1.31704372788576</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.304283695257608</v>
+        <v>1.305834454826273</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.291941910799032</v>
+        <v>1.29449591518722</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.273737094143412</v>
+        <v>1.273424452764229</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.26227285948693</v>
+        <v>1.262657007918887</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.26565840132439</v>
+        <v>1.262574799704639</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.263697779458376</v>
+        <v>1.27425358539285</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36671598369611</v>
+        <v>1.366730007642959</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359272901939424</v>
+        <v>1.359298637287068</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356342052192167</v>
+        <v>1.356373111418858</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350542441349073</v>
+        <v>1.350587169811444</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348252576592386</v>
+        <v>1.348299234840446</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344085829292451</v>
+        <v>1.344134190668515</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339651947320049</v>
+        <v>1.339701336892889</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337196442276107</v>
+        <v>1.33724631874947</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340047759222226</v>
+        <v>1.340080345061143</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334055101767915</v>
+        <v>1.334051426009986</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334967545314126</v>
+        <v>1.334963114321871</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332789560914195</v>
+        <v>1.332784340282359</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332337009653627</v>
+        <v>1.332318765197604</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.32972672125843</v>
+        <v>1.329711614409454</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327906097521572</v>
+        <v>1.327893652261557</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331219636271699</v>
+        <v>1.331209846571647</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329477293583683</v>
+        <v>1.329486299472021</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324393595662364</v>
+        <v>1.324416912630743</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319634592810397</v>
+        <v>1.319667976299387</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319576571476423</v>
+        <v>1.31963880613698</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316715861257457</v>
+        <v>1.31676982026673</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320454328553273</v>
+        <v>1.320495312872819</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318625924169715</v>
+        <v>1.31859765796364</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312893095392161</v>
+        <v>1.312823332284737</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31042194133855</v>
+        <v>1.310312024785251</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.3035149916061</v>
+        <v>1.303380237265717</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293662230963203</v>
+        <v>1.293497760132685</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290065603957257</v>
+        <v>1.289872787395579</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294432975985983</v>
+        <v>1.294242815509621</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310936777697947</v>
+        <v>1.310623213487686</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323607399107443</v>
+        <v>1.323276936842773</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355838593822208</v>
+        <v>1.355657602949298</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374595599107628</v>
+        <v>1.374563159009015</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380338003108344</v>
+        <v>1.380351940065246</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389739183340966</v>
+        <v>1.389805895637481</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391510315516278</v>
+        <v>1.391605818797338</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390112076032567</v>
+        <v>1.390269849748718</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389858586396505</v>
+        <v>1.390070898239518</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394957382484084</v>
+        <v>1.395325853470652</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391422547860442</v>
+        <v>1.391823489244465</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395225844414815</v>
+        <v>1.395664259752741</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377449902313584</v>
+        <v>1.377776826799084</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372516238035202</v>
+        <v>1.372830836987508</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35877727282444</v>
+        <v>1.358970508604903</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339516957704831</v>
+        <v>1.339537655566374</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330155854129673</v>
+        <v>1.330040357834475</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336283839996383</v>
+        <v>1.336207500142588</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338357178722825</v>
+        <v>1.338307880305351</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339137730055788</v>
+        <v>1.339082723248865</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340653285511914</v>
+        <v>1.340637249811707</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340482105171536</v>
+        <v>1.34049533716051</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342683142281448</v>
+        <v>1.342723746264788</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342073622370501</v>
+        <v>1.342114471529473</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343436934663714</v>
+        <v>1.343476983700109</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342673152515528</v>
+        <v>1.341845487836122</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341855607602509</v>
+        <v>1.341480783912727</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343645277505046</v>
+        <v>1.343402577909831</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346804215541844</v>
+        <v>1.34697364082225</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350237201810745</v>
+        <v>1.350384405522512</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351426422521746</v>
+        <v>1.351775400349567</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.349565853059778</v>
+        <v>1.350332463910099</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.3480690811753</v>
+        <v>1.349039241706055</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345378743734077</v>
+        <v>1.345894317788692</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342563290323664</v>
+        <v>1.342630353605625</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340286356850262</v>
+        <v>1.340622515387681</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.33853837782645</v>
+        <v>1.339131513652106</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.338799637087031</v>
+        <v>1.339225793558063</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.336892023981409</v>
+        <v>1.337755610482868</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.335701655887481</v>
+        <v>1.335573887548193</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.333497490712664</v>
+        <v>1.333850886538442</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.331196495258095</v>
+        <v>1.330674942035718</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.326522058394633</v>
+        <v>1.324375839602911</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.31704372788576</v>
+        <v>1.312692098699546</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.305834454826273</v>
+        <v>1.30297255060706</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.29449591518722</v>
+        <v>1.290751618709275</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.273424452764229</v>
+        <v>1.273932781316969</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.262657007918887</v>
+        <v>1.26361248807985</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.262574799704639</v>
+        <v>1.266307046307265</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.27425358539285</v>
+        <v>1.263586133075582</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366730007642959</v>
+        <v>1.366717373447515</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359298637287068</v>
+        <v>1.359275451908206</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356373111418858</v>
+        <v>1.356345128829691</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350587169811444</v>
+        <v>1.350546872246607</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348299234840446</v>
+        <v>1.348257198746984</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344134190668515</v>
+        <v>1.344090620260072</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339701336892889</v>
+        <v>1.339656840179439</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.33724631874947</v>
+        <v>1.337201383337187</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340080345061143</v>
+        <v>1.340050983026603</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334051426009986</v>
+        <v>1.334054735531267</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334963114321871</v>
+        <v>1.334967104185313</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332784340282359</v>
+        <v>1.332789041497831</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332318765197604</v>
+        <v>1.332335199087376</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329711614409454</v>
+        <v>1.329725222787143</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327893652261557</v>
+        <v>1.327904863915983</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331209846571647</v>
+        <v>1.331218666005458</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329486299472021</v>
+        <v>1.329478188908889</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324416912630743</v>
+        <v>1.324395909525347</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319667976299387</v>
+        <v>1.319637904912262</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31963880613698</v>
+        <v>1.319582736708815</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31676982026673</v>
+        <v>1.316721196957005</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320495312872819</v>
+        <v>1.320458372433685</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.31859765796364</v>
+        <v>1.318623109441421</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312823332284737</v>
+        <v>1.312886167069087</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310312024785251</v>
+        <v>1.31041103240681</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303380237265717</v>
+        <v>1.303501622036967</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293497760132685</v>
+        <v>1.293645916740216</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.289872787395579</v>
+        <v>1.290046482237668</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294242815509621</v>
+        <v>1.294414130118276</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310623213487686</v>
+        <v>1.310905735927417</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323276936842773</v>
+        <v>1.323574684697823</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355657602949298</v>
+        <v>1.355820697562083</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374563159009015</v>
+        <v>1.374592395846734</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380351940065246</v>
+        <v>1.380339406792934</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389805895637481</v>
+        <v>1.389745829662174</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391605818797338</v>
+        <v>1.3915198357754</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390269849748718</v>
+        <v>1.390127770339085</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.390070898239518</v>
+        <v>1.389879689224119</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395325853470652</v>
+        <v>1.394993892915422</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391823489244465</v>
+        <v>1.391462256946651</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395664259752741</v>
+        <v>1.395269244316635</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377776826799084</v>
+        <v>1.377482222138194</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372830836987508</v>
+        <v>1.372547316725385</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358970508604903</v>
+        <v>1.358796322106973</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339537655566374</v>
+        <v>1.339518969100521</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330040357834475</v>
+        <v>1.330144429180482</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336207500142588</v>
+        <v>1.336276287608096</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338307880305351</v>
+        <v>1.338352306596083</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339082723248865</v>
+        <v>1.339132304739361</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340637249811707</v>
+        <v>1.340651720013836</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.34049533716051</v>
+        <v>1.340483444546473</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342723746264788</v>
+        <v>1.34268718553979</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342114471529473</v>
+        <v>1.342077683997771</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343476983700109</v>
+        <v>1.343440879303804</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341845487836122</v>
+        <v>1.342677994944015</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341480783912727</v>
+        <v>1.34186015309493</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343402577909831</v>
+        <v>1.343647053305631</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34697364082225</v>
+        <v>1.346802785023403</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350384405522512</v>
+        <v>1.350230079426584</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351775400349567</v>
+        <v>1.351415321351312</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350332463910099</v>
+        <v>1.349552365650748</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349039241706055</v>
+        <v>1.348052068022332</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345894317788692</v>
+        <v>1.345362004628949</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342630353605625</v>
+        <v>1.342559387912481</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340622515387681</v>
+        <v>1.340297707546643</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.339131513652106</v>
+        <v>1.338169914434786</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.339225793558063</v>
+        <v>1.338399496672325</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.337755610482868</v>
+        <v>1.336572221803959</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.335573887548193</v>
+        <v>1.335374632556656</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.333850886538442</v>
+        <v>1.333112326954148</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.330674942035718</v>
+        <v>1.330699540121404</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.324375839602911</v>
+        <v>1.325989749402263</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.312692098699546</v>
+        <v>1.316611808434614</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.30297255060706</v>
+        <v>1.305648906560879</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.290751618709275</v>
+        <v>1.294602690356028</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.273932781316969</v>
+        <v>1.27457699564207</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.26361248807985</v>
+        <v>1.264564540474762</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.266307046307265</v>
+        <v>1.264703928280076</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.263586133075582</v>
+        <v>1.274280937830739</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366717373447515</v>
+        <v>1.366731157155554</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359275451908206</v>
+        <v>1.359300747119234</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356345128829691</v>
+        <v>1.356375658550327</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350546872246607</v>
+        <v>1.350590837716855</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348257198746984</v>
+        <v>1.348303060907913</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344090620260072</v>
+        <v>1.344138156302157</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339656840179439</v>
+        <v>1.339705386806491</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337201383337187</v>
+        <v>1.337250408622329</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340050983026603</v>
+        <v>1.340083021413901</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334054735531267</v>
+        <v>1.33405112667736</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334967104185313</v>
+        <v>1.334962753133625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332789041497831</v>
+        <v>1.332783914404331</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332335199087376</v>
+        <v>1.332317272293611</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329725222787143</v>
+        <v>1.329710377535067</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327904863915983</v>
+        <v>1.327892632449619</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331218666005458</v>
+        <v>1.331209044254182</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329478188908889</v>
+        <v>1.32948703482753</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324395909525347</v>
+        <v>1.324418820696443</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319637904912262</v>
+        <v>1.319670708834315</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319582736708815</v>
+        <v>1.319643909478883</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316721196957005</v>
+        <v>1.316774254631146</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320458372433685</v>
+        <v>1.32049868974124</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318623109441421</v>
+        <v>1.318595354566031</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312886167069087</v>
+        <v>1.312817628817233</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31041103240681</v>
+        <v>1.31030303151989</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303501622036967</v>
+        <v>1.303369207396177</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293645916740216</v>
+        <v>1.293484294309951</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290046482237668</v>
+        <v>1.28985699667395</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294414130118276</v>
+        <v>1.294227229869643</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310905735927417</v>
+        <v>1.310597479744727</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323574684697823</v>
+        <v>1.323249816089982</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355820697562083</v>
+        <v>1.35564272819865</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374592395846734</v>
+        <v>1.374560488614607</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380339406792934</v>
+        <v>1.380353060094163</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389745829662174</v>
+        <v>1.389811328895473</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.3915198357754</v>
+        <v>1.391613591225609</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390127770339085</v>
+        <v>1.390282723121997</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389879689224119</v>
+        <v>1.390088237995833</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394993892915422</v>
+        <v>1.395356060322359</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391462256946651</v>
+        <v>1.391856376510847</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395269244316635</v>
+        <v>1.395700241400955</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377482222138194</v>
+        <v>1.377803701261427</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372547316725385</v>
+        <v>1.372856720720324</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358796322106973</v>
+        <v>1.35898644712657</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339518969100521</v>
+        <v>1.339539391713078</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330144429180482</v>
+        <v>1.330030870549906</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336276287608096</v>
+        <v>1.33620123014079</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338352306596083</v>
+        <v>1.338303826321746</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339132304739361</v>
+        <v>1.339078188891614</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340651720013836</v>
+        <v>1.340635911949132</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340483444546473</v>
+        <v>1.340496393803732</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34268718553979</v>
+        <v>1.34272705510804</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342077683997771</v>
+        <v>1.342117806302089</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343440879303804</v>
+        <v>1.343480290312049</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342677994944015</v>
+        <v>1.341850531057959</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.34186015309493</v>
+        <v>1.341485105891877</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343647053305631</v>
+        <v>1.343404175073196</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346802785023403</v>
+        <v>1.346971575186456</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350230079426584</v>
+        <v>1.35037680503984</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351415321351312</v>
+        <v>1.35176390507945</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.349552365650748</v>
+        <v>1.350319273976938</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348052068022332</v>
+        <v>1.349023441305207</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345362004628949</v>
+        <v>1.345880092296282</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342559387912481</v>
+        <v>1.34262912324313</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340297707546643</v>
+        <v>1.340634936790107</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338169914434786</v>
+        <v>1.338794418609628</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.338399496672325</v>
+        <v>1.338870335981871</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.336572221803959</v>
+        <v>1.337411853334774</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.335374632556656</v>
+        <v>1.335005972110855</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.333112326954148</v>
+        <v>1.33332966536774</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.330699540121404</v>
+        <v>1.330024085525325</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.325989749402263</v>
+        <v>1.323655434736967</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.316611808434614</v>
+        <v>1.312039969194218</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.305648906560879</v>
+        <v>1.302413007523208</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.294602690356028</v>
+        <v>1.29028160998107</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.27457699564207</v>
+        <v>1.274108104920954</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.264564540474762</v>
+        <v>1.264298747531034</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.264703928280076</v>
+        <v>1.266779875793699</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.274280937830739</v>
+        <v>1.264111273317111</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.338870335981871</v>
+        <v>1.338871787393351</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.337411853334774</v>
+        <v>1.337417319437399</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.335005972110855</v>
+        <v>1.335152780126741</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.33332966536774</v>
+        <v>1.333336977617372</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.330024085525325</v>
+        <v>1.330030981727727</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.323655434736967</v>
+        <v>1.323662023482957</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.312039969194218</v>
+        <v>1.312046245489533</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.302413007523208</v>
+        <v>1.302420492381078</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.29028160998107</v>
+        <v>1.290293743395417</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.274108104920954</v>
+        <v>1.274126362493929</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.264298747531034</v>
+        <v>1.26432512464112</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.266779875793699</v>
+        <v>1.266824801847983</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.264111273317111</v>
+        <v>1.264210818617511</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366731157155554</v>
+        <v>1.366718738383928</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359300747119234</v>
+        <v>1.359277956423595</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356375658550327</v>
+        <v>1.35634815080682</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350590837716855</v>
+        <v>1.350551224375574</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348303060907913</v>
+        <v>1.348261738714093</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344138156302157</v>
+        <v>1.344095326018306</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339705386806491</v>
+        <v>1.339661646010301</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337250408622329</v>
+        <v>1.337206236519641</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340083021413901</v>
+        <v>1.340054150425118</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33405112667736</v>
+        <v>1.334054376256966</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334962753133625</v>
+        <v>1.334966671366719</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332783914404331</v>
+        <v>1.332788531797166</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332317272293611</v>
+        <v>1.3323334213997</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329710377535067</v>
+        <v>1.329723751372363</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327892632449619</v>
+        <v>1.327903652401187</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331209044254182</v>
+        <v>1.331217713089851</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32948703482753</v>
+        <v>1.329479067636097</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324418820696443</v>
+        <v>1.324398181391737</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319670708834315</v>
+        <v>1.31964115705212</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319643909478883</v>
+        <v>1.319588792313769</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316774254631146</v>
+        <v>1.316726439861188</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32049868974124</v>
+        <v>1.320462347879408</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318595354566031</v>
+        <v>1.318620347878757</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312817628817233</v>
+        <v>1.312879365638641</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31030303151989</v>
+        <v>1.310400321751061</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303369207396177</v>
+        <v>1.303488494512951</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293484294309951</v>
+        <v>1.293629897089344</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.28985699667395</v>
+        <v>1.29002770488529</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294227229869643</v>
+        <v>1.294395620999666</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310597479744727</v>
+        <v>1.310875241554251</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323249816089982</v>
+        <v>1.323542547136914</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.35564272819865</v>
+        <v>1.355803112347911</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374560488614607</v>
+        <v>1.374589247305637</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380353060094163</v>
+        <v>1.380340780575111</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389811328895473</v>
+        <v>1.389752349763618</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391613591225609</v>
+        <v>1.391529174064045</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390282723121997</v>
+        <v>1.39014317177846</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.390088237995833</v>
+        <v>1.389900401805603</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395356060322359</v>
+        <v>1.395029752448582</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391856376510847</v>
+        <v>1.391501262130188</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395700241400955</v>
+        <v>1.395311879281149</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377803701261427</v>
+        <v>1.377513981583095</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372856720720324</v>
+        <v>1.372577861413355</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35898644712657</v>
+        <v>1.35881505268622</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339539391713078</v>
+        <v>1.339520953067876</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330030870549906</v>
+        <v>1.330133203809905</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33620123014079</v>
+        <v>1.336268867320381</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338303826321746</v>
+        <v>1.338347518608334</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339078188891614</v>
+        <v>1.339126970770843</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340635911949132</v>
+        <v>1.340650177410618</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340496393803732</v>
+        <v>1.340484753993684</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34272705510804</v>
+        <v>1.342691152441396</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342117806302089</v>
+        <v>1.342081670219426</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343480290312049</v>
+        <v>1.343444758703349</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341850531057959</v>
+        <v>1.34268275643114</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341485105891877</v>
+        <v>1.341864625228994</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343404175073196</v>
+        <v>1.343648806509124</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346971575186456</v>
+        <v>1.346801386900351</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.35037680503984</v>
+        <v>1.350223089444117</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.35176390507945</v>
+        <v>1.351404417330917</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350319273976938</v>
+        <v>1.349539103380764</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349023441305207</v>
+        <v>1.348035331832527</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345880092296282</v>
+        <v>1.345345507466381</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.34262912324313</v>
+        <v>1.342555480706238</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340634936790107</v>
+        <v>1.340308790469005</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338794418609628</v>
+        <v>1.338195400991573</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.338871787393351</v>
+        <v>1.338072674865601</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.337417319437399</v>
+        <v>1.33622298771389</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.335152780126741</v>
+        <v>1.335060961702972</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.333336977617372</v>
+        <v>1.332702393041779</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.330030981727727</v>
+        <v>1.330140351988216</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.323662023482957</v>
+        <v>1.325345155890011</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.312046245489533</v>
+        <v>1.316042639208856</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.302420492381078</v>
+        <v>1.305271352640998</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.290293743395417</v>
+        <v>1.294578687316413</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.274126362493929</v>
+        <v>1.275316411744055</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.26432512464112</v>
+        <v>1.26612008026201</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.266824801847983</v>
+        <v>1.266739374034221</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,15 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.264210818617511</v>
+        <v>1.27579159876229</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>1.282611005066248</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366718738383928</v>
+        <v>1.366732287978132</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359277956423595</v>
+        <v>1.35930282270081</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35634815080682</v>
+        <v>1.356378164455863</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350551224375574</v>
+        <v>1.350594446223022</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348261738714093</v>
+        <v>1.348306825001836</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344095326018306</v>
+        <v>1.344142057687766</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339661646010301</v>
+        <v>1.339709371101869</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337206236519641</v>
+        <v>1.337254432234521</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340054150425118</v>
+        <v>1.340085655043656</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334054376256966</v>
+        <v>1.334050832501506</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334966671366719</v>
+        <v>1.334962398115159</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332788531797166</v>
+        <v>1.332783495753096</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.3323334213997</v>
+        <v>1.332315804041011</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329723751372363</v>
+        <v>1.329709160979119</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327903652401187</v>
+        <v>1.327891629263366</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331217713089851</v>
+        <v>1.331208255000163</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329479067636097</v>
+        <v>1.32948775780714</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324398181391737</v>
+        <v>1.324420697267612</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.31964115705212</v>
+        <v>1.319673396371111</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319588792313769</v>
+        <v>1.31964893015396</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316726439861188</v>
+        <v>1.316778618588317</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320462347879408</v>
+        <v>1.3205020142857</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318620347878757</v>
+        <v>1.318593090622357</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312879365638641</v>
+        <v>1.312812020289909</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310400321751061</v>
+        <v>1.310294186911302</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303488494512951</v>
+        <v>1.303358359199454</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293629897089344</v>
+        <v>1.293471049751288</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.29002770488529</v>
+        <v>1.289841464810052</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294395620999666</v>
+        <v>1.294211897871889</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310875241554251</v>
+        <v>1.31057215977444</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323542547136914</v>
+        <v>1.323223131379667</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355803112347911</v>
+        <v>1.355628089497274</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374589247305637</v>
+        <v>1.374557859973848</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380340780575111</v>
+        <v>1.380354158616698</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389752349763618</v>
+        <v>1.389816668638316</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391529174064045</v>
+        <v>1.39162122901758</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.39014317177846</v>
+        <v>1.390295378426764</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389900401805603</v>
+        <v>1.390105286450466</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395029752448582</v>
+        <v>1.395385776578739</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391501262130188</v>
+        <v>1.391888732375774</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395311879281149</v>
+        <v>1.395735644709022</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377513981583095</v>
+        <v>1.377830150143345</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372577861413355</v>
+        <v>1.372882197874784</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35881505268622</v>
+        <v>1.359002141194885</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339520953067876</v>
+        <v>1.339541105505321</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330133203809905</v>
+        <v>1.330021534538492</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336268867320381</v>
+        <v>1.336195060239687</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338347518608334</v>
+        <v>1.338299836330242</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339126970770843</v>
+        <v>1.339073724484829</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340650177410618</v>
+        <v>1.340634592373379</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340484753993684</v>
+        <v>1.34049742912806</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342691152441396</v>
+        <v>1.342730307280844</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342081670219426</v>
+        <v>1.342121084835287</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343444758703349</v>
+        <v>1.34348354667096</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34268275643114</v>
+        <v>1.34185549570963</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341864625228994</v>
+        <v>1.34148936288504</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343648806509124</v>
+        <v>1.343405753196752</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346801386900351</v>
+        <v>1.346969549273484</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350223089444117</v>
+        <v>1.350369334093334</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351404417330917</v>
+        <v>1.351752595877886</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.349539103380764</v>
+        <v>1.350306281158913</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348035331832527</v>
+        <v>1.349007868330543</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345345507466381</v>
+        <v>1.345866043765938</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342555480706238</v>
+        <v>1.342627844372071</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340308790469005</v>
+        <v>1.34064709344146</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338195400991573</v>
+        <v>1.338818739340364</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.338072674865601</v>
+        <v>1.338575512121986</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.33622298771389</v>
+        <v>1.337112844599379</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.335060961702972</v>
+        <v>1.334893553530034</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.332702393041779</v>
+        <v>1.332972227803265</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.330140351988216</v>
+        <v>1.329558467369619</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.325345155890011</v>
+        <v>1.323133439369491</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.316042639208856</v>
+        <v>1.31164099154448</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.305271352640998</v>
+        <v>1.302151168528248</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.294578687316413</v>
+        <v>1.290428081236383</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.275316411744055</v>
+        <v>1.274790183837208</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.26612008026201</v>
+        <v>1.265690778268645</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.266739374034221</v>
+        <v>1.26833010527754</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.27579159876229</v>
+        <v>1.267072325872074</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>1.282611005066248</v>
+        <v>1.278351416935448</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366732287978132</v>
+        <v>1.366720079164082</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35930282270081</v>
+        <v>1.359280416690103</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356378164455863</v>
+        <v>1.356351119567238</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350594446223022</v>
+        <v>1.35055549981761</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348306825001836</v>
+        <v>1.3482661986662</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344142057687766</v>
+        <v>1.344099948820054</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339709371101869</v>
+        <v>1.339666367113818</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337254432234521</v>
+        <v>1.33721100414694</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.340085655043656</v>
+        <v>1.340057262884413</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334050832501506</v>
+        <v>1.334054023749039</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334962398115159</v>
+        <v>1.334966246626316</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332783495753096</v>
+        <v>1.332788031542659</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332315804041011</v>
+        <v>1.332331675703514</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329709160979119</v>
+        <v>1.329722306288242</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327891629263366</v>
+        <v>1.327902462389177</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331208255000163</v>
+        <v>1.331216777063719</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32948775780714</v>
+        <v>1.329479930221941</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324420697267612</v>
+        <v>1.324400412393708</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319673396371111</v>
+        <v>1.319644350842532</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31964893015396</v>
+        <v>1.319594741188757</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316778618588317</v>
+        <v>1.31673159236711</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.3205020142857</v>
+        <v>1.320466256607054</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318593090622357</v>
+        <v>1.318617637995227</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312812020289909</v>
+        <v>1.312872687652021</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310294186911302</v>
+        <v>1.310389804021884</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303358359199454</v>
+        <v>1.303475602529578</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293471049751288</v>
+        <v>1.293614164115954</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.289841464810052</v>
+        <v>1.290009262695575</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294211897871889</v>
+        <v>1.294377439693864</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31057215977444</v>
+        <v>1.310845280239456</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323223131379667</v>
+        <v>1.323510971315211</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355628089497274</v>
+        <v>1.355785830150903</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374557859973848</v>
+        <v>1.374586152101648</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380354158616698</v>
+        <v>1.380342125379098</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389816668638316</v>
+        <v>1.389758747194244</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39162122901758</v>
+        <v>1.391538335521215</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390295378426764</v>
+        <v>1.390158288444269</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.390105286450466</v>
+        <v>1.389920734832256</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395385776578739</v>
+        <v>1.395064978313052</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.391888732375774</v>
+        <v>1.391539581933419</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.395735644709022</v>
+        <v>1.395353769327744</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377830150143345</v>
+        <v>1.377545195072004</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372882197874784</v>
+        <v>1.372607885712034</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.359002141194885</v>
+        <v>1.358833472457423</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339541105505321</v>
+        <v>1.339522910119209</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330021534538492</v>
+        <v>1.330122172843415</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336195060239687</v>
+        <v>1.336261575705044</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338299836330242</v>
+        <v>1.338342812606298</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339073724484829</v>
+        <v>1.339121725872749</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340634592373379</v>
+        <v>1.34064865722802</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.34049742912806</v>
+        <v>1.340486034463604</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342730307280844</v>
+        <v>1.342695045120228</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.342121084835287</v>
+        <v>1.342085583107098</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34348354667096</v>
+        <v>1.343448574450337</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34185549570963</v>
+        <v>1.342687438977536</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.34148936288504</v>
+        <v>1.341869025744744</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343405753196752</v>
+        <v>1.343650537482509</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346969549273484</v>
+        <v>1.34680002014972</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350369334093334</v>
+        <v>1.350216228244552</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351752595877886</v>
+        <v>1.351393705312468</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350306281158913</v>
+        <v>1.349526060754443</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.349007868330543</v>
+        <v>1.348018866047335</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345866043765938</v>
+        <v>1.345329247382116</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342627844372071</v>
+        <v>1.342551570713164</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.34064709344146</v>
+        <v>1.340319614213725</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338818739340364</v>
+        <v>1.338220408180411</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.338575512121986</v>
+        <v>1.337813585970551</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.337112844599379</v>
+        <v>1.335943130885465</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.334893553530034</v>
+        <v>1.334805834710915</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.332972227803265</v>
+        <v>1.332371196411198</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.329558467369619</v>
+        <v>1.329672551282381</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.323133439369491</v>
+        <v>1.324824570858128</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.31164099154448</v>
+        <v>1.315615095468571</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.302151168528248</v>
+        <v>1.305062522803575</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.290428081236383</v>
+        <v>1.294737107693441</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.274790183837208</v>
+        <v>1.276243426836594</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.265690778268645</v>
+        <v>1.267834042154593</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.26833010527754</v>
+        <v>1.268945238721233</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.267072325872074</v>
+        <v>1.277747374738762</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>1.278351416935448</v>
+        <v>1.285729451144629</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,962 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>44743</v>
       </c>
       <c r="B2">
-        <v>1.32324</v>
+        <v>1.231545454545454</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>44778</v>
       </c>
       <c r="B3">
-        <v>1.32286785188864</v>
+        <v>1.228533488179552</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>44806</v>
       </c>
       <c r="B4">
-        <v>1.321539875383601</v>
+        <v>1.224201228536688</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>44834</v>
       </c>
       <c r="B5">
-        <v>1.317915132681427</v>
+        <v>1.174613486050007</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>44869</v>
       </c>
       <c r="B6">
-        <v>1.312828815943879</v>
+        <v>1.173593520353622</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>44897</v>
       </c>
       <c r="B7">
-        <v>1.306588254763449</v>
+        <v>1.170739163579364</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>44932</v>
       </c>
       <c r="B8">
-        <v>1.298896139388236</v>
+        <v>1.188411979102264</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>44960</v>
       </c>
       <c r="B9">
-        <v>1.292031851536083</v>
+        <v>1.181539778549158</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>44988</v>
       </c>
       <c r="B10">
-        <v>1.286698569117303</v>
+        <v>1.175426058883731</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45016</v>
       </c>
       <c r="B11">
-        <v>1.280785998059444</v>
+        <v>1.181273782659546</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45051</v>
       </c>
       <c r="B12">
-        <v>1.277725971840549</v>
+        <v>1.215899288453202</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45079</v>
       </c>
       <c r="B13">
-        <v>1.275743461528499</v>
+        <v>1.215242064475422</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45107</v>
       </c>
       <c r="B14">
-        <v>1.272232406747641</v>
+        <v>1.230813497740191</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45142</v>
+      </c>
+      <c r="B15">
+        <v>1.238023878638678</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45170</v>
+      </c>
+      <c r="B16">
+        <v>1.22734473454327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45205</v>
+      </c>
+      <c r="B17">
+        <v>1.22368736878921</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45233</v>
+      </c>
+      <c r="B18">
+        <v>1.230684599245121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45261</v>
+      </c>
+      <c r="B19">
+        <v>1.235306890517007</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45296</v>
+      </c>
+      <c r="B20">
+        <v>1.246113596473587</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45324</v>
+      </c>
+      <c r="B21">
+        <v>1.253356726564096</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45352</v>
+      </c>
+      <c r="B22">
+        <v>1.250342779833523</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45387</v>
+      </c>
+      <c r="B23">
+        <v>1.247355830572833</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45415</v>
+      </c>
+      <c r="B24">
+        <v>1.260416046296522</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45443</v>
+      </c>
+      <c r="B25">
+        <v>1.253272305723553</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45478</v>
+      </c>
+      <c r="B26">
+        <v>1.260851512842389</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45506</v>
+      </c>
+      <c r="B27">
+        <v>1.260575226412116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45541</v>
+      </c>
+      <c r="B28">
+        <v>1.26626228493893</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>45569</v>
+      </c>
+      <c r="B29">
+        <v>1.30356882492954</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>45597</v>
+      </c>
+      <c r="B30">
+        <v>1.297639608383179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>45632</v>
+      </c>
+      <c r="B31">
+        <v>1.268793940544128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>45660</v>
+      </c>
+      <c r="B32">
+        <v>1.249796867370605</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>45688</v>
+      </c>
+      <c r="B33">
+        <v>1.253067617849758</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>45716</v>
+      </c>
+      <c r="B34">
+        <v>1.242652773857117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>45751</v>
+      </c>
+      <c r="B35">
+        <v>1.28541261604673</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>45779</v>
+      </c>
+      <c r="B36">
+        <v>1.3046</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>45814</v>
+      </c>
+      <c r="B37">
+        <v>1.3525</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>45821</v>
+      </c>
+      <c r="B38">
+        <v>1.36214463902828</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>45828</v>
+      </c>
+      <c r="B39">
+        <v>1.35217376749137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>45835</v>
+      </c>
+      <c r="B40">
+        <v>1.381257103810299</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>45842</v>
+      </c>
+      <c r="B41">
+        <v>1.37154856208649</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>45849</v>
+      </c>
+      <c r="B42">
+        <v>1.366721396423604</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>45856</v>
+      </c>
+      <c r="B43">
+        <v>1.35928283387006</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>45863</v>
+      </c>
+      <c r="B44">
+        <v>1.356354036504235</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B45">
+        <v>1.350559700581651</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>45877</v>
+      </c>
+      <c r="B46">
+        <v>1.3482705806999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>45884</v>
+      </c>
+      <c r="B47">
+        <v>1.344104490839497</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>45891</v>
+      </c>
+      <c r="B48">
+        <v>1.33967100571076</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>45898</v>
+      </c>
+      <c r="B49">
+        <v>1.337215688461371</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B50">
+        <v>1.34006032182075</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B51">
+        <v>1.334053677818781</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B52">
+        <v>1.334965829740612</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B53">
+        <v>1.332787540474634</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B54">
+        <v>1.332329961143347</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B55">
+        <v>1.329720886834653</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B56">
+        <v>1.327901293312625</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B57">
+        <v>1.331215857482097</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B58">
+        <v>1.329480777106477</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B59">
+        <v>1.324402603623132</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B60">
+        <v>1.31964748783879</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B61">
+        <v>1.319600586130061</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B62">
+        <v>1.316736656790115</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B63">
+        <v>1.320470100276516</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B64">
+        <v>1.318614978359057</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B65">
+        <v>1.312866129784096</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B66">
+        <v>1.310379474060323</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B67">
+        <v>1.303462939813038</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B68">
+        <v>1.293598710204604</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B69">
+        <v>1.2899911467886</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B70">
+        <v>1.294359577577669</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B71">
+        <v>1.310815838140034</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B72">
+        <v>1.323479942645832</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B73">
+        <v>1.355768843215864</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B74">
+        <v>1.374583108898</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B75">
+        <v>1.380343442092059</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B76">
+        <v>1.389765025371616</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B77">
+        <v>1.391547325095144</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B78">
+        <v>1.390173128135518</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B79">
+        <v>1.389940698609517</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B80">
+        <v>1.395099587136326</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B81">
+        <v>1.39157723423553</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B82">
+        <v>1.39539493378422</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B83">
+        <v>1.377575876538732</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B84">
+        <v>1.372637402776703</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B85">
+        <v>1.358851589058489</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B86">
+        <v>1.339524840756094</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B87">
+        <v>1.330111331283492</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B88">
+        <v>1.33625440945123</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B89">
+        <v>1.338338186509278</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B90">
+        <v>1.339116567842308</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B91">
+        <v>1.340647159003789</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B92">
+        <v>1.340487286867987</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B93">
+        <v>1.342698865631749</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B94">
+        <v>1.34208942465752</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B95">
+        <v>1.343452328082273</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B96">
+        <v>1.342692044518858</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B97">
+        <v>1.34187335632841</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B98">
+        <v>1.343652246587706</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B99">
+        <v>1.346798683789479</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B100">
+        <v>1.350209492338533</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>1.351383180323636</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>1.349513232450402</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>1.348002664308249</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>1.345313219627451</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>1.342547659809627</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>1.340330187032715</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>1.338244949024455</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>1.337514371028333</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>1.335622676306489</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>1.334518495682695</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>1.332005680662132</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>1.329187099745148</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>1.324283751374476</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>1.315167586600878</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>1.304804057492244</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>1.294786932637626</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>1.276914156231582</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>1.269061161281028</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>1.270308201790088</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>1.268398299068151</v>
+      <c r="B120">
+        <v>1.278317776350821</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>1.284229722022819</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366721396423604</v>
+        <v>1.366722690776012</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35928283387006</v>
+        <v>1.359285209085441</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356354036504235</v>
+        <v>1.356356902962889</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350559700581651</v>
+        <v>1.350563828607077</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.3482705806999</v>
+        <v>1.348274886839189</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.344104490839497</v>
+        <v>1.34410895417551</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33967100571076</v>
+        <v>1.339675563944972</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337215688461371</v>
+        <v>1.337220291627556</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.34006032182075</v>
+        <v>1.340063328602159</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334053677818781</v>
+        <v>1.334053338284415</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334965829740612</v>
+        <v>1.334965420494264</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332787540474634</v>
+        <v>1.332787058342828</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332329961143347</v>
+        <v>1.332328276893943</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329720886834653</v>
+        <v>1.329719492336059</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327901293312625</v>
+        <v>1.327900144623985</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331215857482097</v>
+        <v>1.331214953915511</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329480777106477</v>
+        <v>1.329481608713933</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324402603623132</v>
+        <v>1.324404756133353</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.31964748783879</v>
+        <v>1.319650569541435</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319600586130061</v>
+        <v>1.319606329837155</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316736656790115</v>
+        <v>1.316741635367237</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320470100276516</v>
+        <v>1.320473880493282</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318614978359057</v>
+        <v>1.3186123675907</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.312866129784096</v>
+        <v>1.312859688827917</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310379474060323</v>
+        <v>1.310369326889492</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303462939813038</v>
+        <v>1.303450500310064</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.293598710204604</v>
+        <v>1.293583528006828</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.2899911467886</v>
+        <v>1.289973348594905</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294359577577669</v>
+        <v>1.294342026327391</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.310815838140034</v>
+        <v>1.310786901887743</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.323479942645832</v>
+        <v>1.323449447042136</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.355768843215864</v>
+        <v>1.355752144049652</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374583108898</v>
+        <v>1.374580116401966</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380343442092059</v>
+        <v>1.38034473156591</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389765025371616</v>
+        <v>1.389771187587918</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391547325095144</v>
+        <v>1.391556147552028</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.390173128135518</v>
+        <v>1.390187698369885</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389940698609517</v>
+        <v>1.389960303074168</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.395099587136326</v>
+        <v>1.395133594969938</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.39157723423553</v>
+        <v>1.391614236300162</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.39539493378422</v>
+        <v>1.395435391316358</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.377575876538732</v>
+        <v>1.377606039447764</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.372637402776703</v>
+        <v>1.372666425324026</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358851589058489</v>
+        <v>1.358869409880331</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339524840756094</v>
+        <v>1.339526745469534</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330111331283492</v>
+        <v>1.330100674302134</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33625440945123</v>
+        <v>1.336247365360455</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338338186509278</v>
+        <v>1.338333638306142</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339116567842308</v>
+        <v>1.339111494548444</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340647159003789</v>
+        <v>1.340645682287341</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340487286867987</v>
+        <v>1.340488512081814</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342698865631749</v>
+        <v>1.342702615956495</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34208942465752</v>
+        <v>1.342093196795863</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343452328082273</v>
+        <v>1.343456021088146</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342692044518858</v>
+        <v>1.342696574928378</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.34187335632841</v>
+        <v>1.341877618614439</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343652246587706</v>
+        <v>1.343653934181471</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346798683789479</v>
+        <v>1.346797376876561</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350209492338533</v>
+        <v>1.350202878360451</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351383180323636</v>
+        <v>1.351372837560489</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.349513232450402</v>
+        <v>1.349500613314575</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348002664308249</v>
+        <v>1.347986720449482</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345313219627451</v>
+        <v>1.345297419566575</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342547659809627</v>
+        <v>1.342543749748287</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340330187032715</v>
+        <v>1.34034051684983</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338244949024455</v>
+        <v>1.338269036091346</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.337514371028333</v>
+        <v>1.33744960562998</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.335622676306489</v>
+        <v>1.335580553471019</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.334518495682695</v>
+        <v>1.334508670589232</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.332005680662132</v>
+        <v>1.331975910119884</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.329187099745148</v>
+        <v>1.329093165301603</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.324283751374476</v>
+        <v>1.324202324204501</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.315167586600878</v>
+        <v>1.315253820305984</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.304804057492244</v>
+        <v>1.305182459356138</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>1.294786932637626</v>
+        <v>1.295595681223695</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>1.276914156231582</v>
+        <v>1.278551878168626</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>1.269061161281028</v>
+        <v>1.271496261659125</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>1.270308201790088</v>
+        <v>1.273343207449099</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>1.278317776350821</v>
+        <v>1.281684876524066</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>1.284229722022819</v>
+        <v>1.290123749637353</v>
       </c>
     </row>
   </sheetData>
